--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10028.69</v>
+        <v>10029.84</v>
       </c>
       <c r="C5" s="2">
         <f>B5-B4</f>
@@ -784,7 +784,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>180.97</v>
+        <v>181.27</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2562034240276834</v>
+        <v>0.257160996221582</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1086562815531136</v>
+        <v>0.1095013822808306</v>
       </c>
       <c r="H2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>45.92</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="3">
@@ -1158,19 +1158,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4397722833411737</v>
+        <v>0.4419624064329755</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1126029974749743</v>
+        <v>0.1142954439437471</v>
       </c>
       <c r="H3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>197.22</v>
+        <v>197.52</v>
       </c>
     </row>
     <row r="4">
@@ -1193,19 +1193,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.113</v>
+        <v>0.112</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1925333841179526</v>
+        <v>0.1914650325755531</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.04413661686626402</v>
+        <v>0.04320120912006487</v>
       </c>
       <c r="H4" t="n">
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>66.98</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="5">
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.107</v>
+        <v>0.111</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2598103824043456</v>
+        <v>0.2659118926098922</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1844807007064677</v>
+        <v>0.1902173744032192</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I5" t="n">
-        <v>78.45999999999999</v>
+        <v>78.84</v>
       </c>
     </row>
     <row r="6">
@@ -1266,16 +1266,16 @@
         <v>0.105</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3802695514444174</v>
+        <v>0.3805355556508698</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.07843134058217127</v>
+        <v>0.07863917482198679</v>
       </c>
       <c r="H6" t="n">
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>545.05</v>
+        <v>545.16</v>
       </c>
     </row>
     <row r="7">
@@ -1301,16 +1301,16 @@
         <v>0.103</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2172283684946499</v>
+        <v>0.2164273846565206</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.05869882683502237</v>
+        <v>0.05800216163094896</v>
       </c>
       <c r="H7" t="n">
         <v>0.93</v>
       </c>
       <c r="I7" t="n">
-        <v>174.77</v>
+        <v>174.65</v>
       </c>
     </row>
     <row r="8">
@@ -1333,19 +1333,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.5531609000358768</v>
+        <v>0.5503140223782654</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.198723653474137</v>
+        <v>0.1965264441659145</v>
       </c>
       <c r="H8" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>207.75</v>
+        <v>207.37</v>
       </c>
     </row>
     <row r="9">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1437006220014818</v>
+        <v>0.1441302441186731</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.02565718073004097</v>
+        <v>0.02604246075964056</v>
       </c>
       <c r="H9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>79.86</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="10">
@@ -1403,19 +1403,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.108859091730475</v>
+        <v>0.1097620976666909</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.04740462748558105</v>
+        <v>0.04825758761666799</v>
       </c>
       <c r="H10" t="n">
         <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>393.07</v>
+        <v>393.39</v>
       </c>
     </row>
     <row r="11">
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1195868020001469</v>
+        <v>0.1203444822881137</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1460121794054672</v>
+        <v>0.1467877430656983</v>
       </c>
       <c r="H11" t="n">
         <v>1.15</v>
       </c>
       <c r="I11" t="n">
-        <v>762.1799999999999</v>
+        <v>762.7</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10029.84</v>
+        <v>10029.01</v>
       </c>
       <c r="C5" s="2">
         <f>B5-B4</f>
@@ -784,7 +784,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>181.27</v>
+        <v>181.03</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1158,19 +1158,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4419624064329755</v>
+        <v>0.4402102856806764</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1142954439437471</v>
+        <v>0.1129414695524482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>197.52</v>
+        <v>197.28</v>
       </c>
     </row>
     <row r="4">
@@ -1193,19 +1193,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1914650325755531</v>
+        <v>0.1903078441725397</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.04320120912006487</v>
+        <v>0.04218801921671234</v>
       </c>
       <c r="H4" t="n">
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>66.92</v>
+        <v>66.86</v>
       </c>
     </row>
     <row r="5">
@@ -1266,16 +1266,16 @@
         <v>0.105</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3805355556508698</v>
+        <v>0.3801429637366405</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.07863917482198679</v>
+        <v>0.07833243515369448</v>
       </c>
       <c r="H6" t="n">
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>545.16</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7">
@@ -1298,19 +1298,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2164273846565206</v>
+        <v>0.2140245394156952</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.05800216163094896</v>
+        <v>0.05591225845142156</v>
       </c>
       <c r="H7" t="n">
         <v>0.93</v>
       </c>
       <c r="I7" t="n">
-        <v>174.65</v>
+        <v>174.31</v>
       </c>
     </row>
     <row r="8">
@@ -1336,16 +1336,16 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.5503140223782654</v>
+        <v>0.5506975454863312</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1965264441659145</v>
+        <v>0.1968224458366248</v>
       </c>
       <c r="H8" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>207.37</v>
+        <v>207.42</v>
       </c>
     </row>
     <row r="9">
@@ -1406,16 +1406,16 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1097620976666909</v>
+        <v>0.1096207366458817</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.04825758761666799</v>
+        <v>0.04812406101401345</v>
       </c>
       <c r="H10" t="n">
         <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>393.39</v>
+        <v>393.34</v>
       </c>
     </row>
     <row r="11">
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1203444822881137</v>
+        <v>0.1181420004570648</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1467877430656983</v>
+        <v>0.1445332765082217</v>
       </c>
       <c r="H11" t="n">
         <v>1.15</v>
       </c>
       <c r="I11" t="n">
-        <v>762.7</v>
+        <v>761.2</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,6 +82,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -154,12 +164,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>0</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -179,12 +189,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -204,12 +214,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -519,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -599,7 +609,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10002.9</v>
+        <v>10038.05</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -611,28 +621,6 @@
       </c>
       <c r="E4" s="3">
         <f>B4/$B$2-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>10029.01</v>
-      </c>
-      <c r="C5" s="2">
-        <f>B5-B4</f>
-        <v/>
-      </c>
-      <c r="D5" s="3">
-        <f>B5/B4-1</f>
-        <v/>
-      </c>
-      <c r="E5" s="3">
-        <f>B5/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -645,12 +633,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Grafieken van vandaag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Shell (SHELL.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>SAP (SAP.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -745,7 +774,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.24</v>
+        <v>43.73</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -784,7 +813,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>181.03</v>
+        <v>182</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1123,19 +1152,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.172</v>
+        <v>0.152</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.257160996221582</v>
+        <v>0.233556455119823</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1095013822808306</v>
+        <v>0.0879391335134192</v>
       </c>
       <c r="H2" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>45.95</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="3">
@@ -1158,19 +1187,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.121</v>
+        <v>0.113</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4402102856806764</v>
+        <v>0.4360498853544057</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1129414695524482</v>
+        <v>0.05869144547825433</v>
       </c>
       <c r="H3" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>197.28</v>
+        <v>198.06</v>
       </c>
     </row>
     <row r="4">
@@ -1179,33 +1208,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>WKL.AS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.111</v>
+        <v>0.106</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1903078441725397</v>
+        <v>0.2847465402917702</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.04218801921671234</v>
+        <v>0.1391962364023651</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>66.86</v>
+        <v>78.23999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1214,33 +1243,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WKL.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.111</v>
+        <v>0.101</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2659118926098922</v>
+        <v>0.3544897381562548</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1902173744032192</v>
+        <v>0.09081312354094284</v>
       </c>
       <c r="H5" t="n">
-        <v>1.19</v>
+        <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>78.84</v>
+        <v>542.27</v>
       </c>
     </row>
     <row r="6">
@@ -1249,12 +1278,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1263,19 +1292,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3801429637366405</v>
+        <v>0.1874796421431999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.07833243515369448</v>
+        <v>0.02699966183633928</v>
       </c>
       <c r="H6" t="n">
-        <v>0.82</v>
+        <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>545</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="7">
@@ -1298,19 +1327,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.101</v>
+        <v>0.093</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2140245394156952</v>
+        <v>0.207873609596017</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.05591225845142156</v>
+        <v>0.03446132295461757</v>
       </c>
       <c r="H7" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I7" t="n">
-        <v>174.31</v>
+        <v>175.15</v>
       </c>
     </row>
     <row r="8">
@@ -1336,16 +1365,16 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.5506975454863312</v>
+        <v>0.5443692073011557</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1968224458366248</v>
+        <v>0.2032046994524308</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>207.42</v>
+        <v>207.62</v>
       </c>
     </row>
     <row r="9">
@@ -1368,19 +1397,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1441302441186731</v>
+        <v>0.1491090634693417</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.02604246075964056</v>
+        <v>0.006630444465604679</v>
       </c>
       <c r="H9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>79.89</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="10">
@@ -1403,19 +1432,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.059</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1096207366458817</v>
+        <v>0.08222255213028928</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.04812406101401345</v>
+        <v>0.05007719983789816</v>
       </c>
       <c r="H10" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>393.34</v>
+        <v>394.43</v>
       </c>
     </row>
     <row r="11">
@@ -1438,19 +1467,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1181420004570648</v>
+        <v>0.1303343239971699</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1445332765082217</v>
+        <v>0.1207214036696838</v>
       </c>
       <c r="H11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I11" t="n">
-        <v>761.2</v>
+        <v>750.5599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10038.05</v>
+        <v>10038.91</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -774,7 +774,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.73</v>
+        <v>43.79</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>182</v>
+        <v>182.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1152,19 +1152,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.152</v>
+        <v>0.154</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.233556455119823</v>
+        <v>0.2350168204876995</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0879391335134192</v>
+        <v>0.0892271075062967</v>
       </c>
       <c r="H2" t="n">
         <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>46.46</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="3">
@@ -1190,16 +1190,16 @@
         <v>0.113</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4360498853544057</v>
+        <v>0.4374999792559238</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.05869144547825433</v>
+        <v>0.05976049051933141</v>
       </c>
       <c r="H3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>198.06</v>
+        <v>198.26</v>
       </c>
     </row>
     <row r="4">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2847465402917702</v>
+        <v>0.2873738940359121</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1391962364023651</v>
+        <v>0.1415259344425281</v>
       </c>
       <c r="H4" t="n">
         <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>78.23999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1260,16 +1260,16 @@
         <v>0.101</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.3544897381562548</v>
+        <v>0.3539276333076167</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.09081312354094284</v>
+        <v>0.09036044285357536</v>
       </c>
       <c r="H5" t="n">
         <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>542.27</v>
+        <v>542.04</v>
       </c>
     </row>
     <row r="6">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1874796421431999</v>
+        <v>0.1885382506968107</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.02699966183633928</v>
+        <v>0.02791520648063583</v>
       </c>
       <c r="H6" t="n">
         <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>67.31</v>
+        <v>67.37</v>
       </c>
     </row>
     <row r="7">
@@ -1327,19 +1327,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.207873609596017</v>
+        <v>0.2090115129853465</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.03446132295461757</v>
+        <v>0.0354358595585873</v>
       </c>
       <c r="H7" t="n">
         <v>0.92</v>
       </c>
       <c r="I7" t="n">
-        <v>175.15</v>
+        <v>175.32</v>
       </c>
     </row>
     <row r="8">
@@ -1365,16 +1365,16 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.5443692073011557</v>
+        <v>0.5470061266692847</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2032046994524308</v>
+        <v>0.2052591005378777</v>
       </c>
       <c r="H8" t="n">
         <v>0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>207.62</v>
+        <v>207.98</v>
       </c>
     </row>
     <row r="9">
@@ -1397,19 +1397,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1491090634693417</v>
+        <v>0.1505439233170964</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.006630444465604679</v>
+        <v>0.007887395308834755</v>
       </c>
       <c r="H9" t="n">
         <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>80.09</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="10">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.08222255213028928</v>
+        <v>0.08275760607653826</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05007719983789816</v>
+        <v>0.0505963610294049</v>
       </c>
       <c r="H10" t="n">
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>394.43</v>
+        <v>394.62</v>
       </c>
     </row>
     <row r="11">
@@ -1470,16 +1470,16 @@
         <v>0.058</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1303343239971699</v>
+        <v>0.1306204653874163</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1207214036696838</v>
+        <v>0.1210051115724846</v>
       </c>
       <c r="H11" t="n">
         <v>1.14</v>
       </c>
       <c r="I11" t="n">
-        <v>750.5599999999999</v>
+        <v>750.75</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,11 +39,16 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="16"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -84,6 +89,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -169,7 +175,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -191,10 +197,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -216,10 +222,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -529,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -609,7 +615,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10038.91</v>
+        <v>10014.42</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -621,6 +627,28 @@
       </c>
       <c r="E4" s="3">
         <f>B4/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>10026.44</v>
+      </c>
+      <c r="C5" s="2">
+        <f>B5-B4</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>B5/B4-1</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>B5/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -635,14 +663,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B66"/>
+  <dimension ref="B1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="130" customWidth="1" min="2" max="2"/>
+    <col width="128" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Grafieken van vandaag</t>
@@ -650,33 +678,39 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Shell (SHELL.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>SAP (SAP.DE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Microsoft (MSFT)</t>
-        </is>
-      </c>
-    </row>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>1. Shell (SHELL.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="402" customHeight="1"/>
+    <row r="6" ht="30" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>2. SAP (SAP.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="402" customHeight="1"/>
+    <row r="9" ht="30" customHeight="1"/>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>3. Microsoft (MSFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="402" customHeight="1"/>
+    <row r="12" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -774,7 +808,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.79</v>
+        <v>43.73</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -813,7 +847,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>182.2</v>
+        <v>181.04</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1152,19 +1186,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.154</v>
+        <v>0.155</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2350168204876995</v>
+        <v>0.233556455119823</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0892271075062967</v>
+        <v>0.0879391335134192</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>46.51</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="3">
@@ -1187,19 +1221,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4374999792559238</v>
+        <v>0.4279292709978453</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.05976049051933141</v>
+        <v>0.05270472799789561</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>198.26</v>
+        <v>196.94</v>
       </c>
     </row>
     <row r="4">
@@ -1222,19 +1256,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2873738940359121</v>
+        <v>0.2817908299691714</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1415259344425281</v>
+        <v>0.1365753816502397</v>
       </c>
       <c r="H4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="n">
-        <v>78.40000000000001</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="5">
@@ -1243,12 +1277,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1257,19 +1291,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.101</v>
+        <v>0.106</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.3539276333076167</v>
+        <v>0.1931250609053237</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.09036044285357536</v>
+        <v>0.03188213977858134</v>
       </c>
       <c r="H5" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="I5" t="n">
-        <v>542.04</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="6">
@@ -1278,12 +1312,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1295,16 +1329,16 @@
         <v>0.101</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1885382506968107</v>
+        <v>0.2206657103115155</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.02791520648063583</v>
+        <v>0.04541688430175994</v>
       </c>
       <c r="H6" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="I6" t="n">
-        <v>67.37</v>
+        <v>177.01</v>
       </c>
     </row>
     <row r="7">
@@ -1313,12 +1347,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1327,19 +1361,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2090115129853465</v>
+        <v>0.3330707534804345</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.0354358595585873</v>
+        <v>0.07356374252377029</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="I7" t="n">
-        <v>175.32</v>
+        <v>533.6900000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1348,33 +1382,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TTE.PA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.5470061266692847</v>
+        <v>0.1502569075617706</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2052591005378777</v>
+        <v>0.007635966783434256</v>
       </c>
       <c r="H8" t="n">
-        <v>0.68</v>
+        <v>1.12</v>
       </c>
       <c r="I8" t="n">
-        <v>207.98</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="9">
@@ -1383,33 +1417,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TTE.PA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1505439233170964</v>
+        <v>0.4948675808622736</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.007887395308834755</v>
+        <v>0.1646384101996907</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="I9" t="n">
-        <v>80.19</v>
+        <v>200.97</v>
       </c>
     </row>
     <row r="10">
@@ -1418,12 +1452,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1432,19 +1466,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.06</v>
+        <v>0.053</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.08275760607653826</v>
+        <v>0.1107263312675328</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.0505963610294049</v>
+        <v>0.101280166976637</v>
       </c>
       <c r="H10" t="n">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>394.62</v>
+        <v>737.54</v>
       </c>
     </row>
     <row r="11">
@@ -1453,12 +1487,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1467,19 +1501,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1306204653874163</v>
+        <v>0.07399126212527274</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1210051115724846</v>
+        <v>0.04209040456874846</v>
       </c>
       <c r="H11" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>750.75</v>
+        <v>391.43</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trends" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafiekdata" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,7 +49,12 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000B0B0B"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="0052514E"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -88,8 +94,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -166,81 +175,864 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$B$2:$B$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$C$2:$C$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$D$2:$D$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$E$2:$E$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$F$2:$F$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="47.5"/>
+          <min val="32.5"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers EUR</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="2.5"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$I$2:$I$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$J$2:$J$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$L$2:$L$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$M$2:$M$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="220"/>
+          <min val="120"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers EUR</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="20"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!P1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$O$2:$O$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$P$2:$P$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!Q1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$O$2:$O$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$Q$2:$Q$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!R1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$O$2:$O$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$R$2:$R$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!S1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$O$2:$O$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$S$2:$S$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!T1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$O$2:$O$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$T$2:$T$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="600"/>
+          <min val="350"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="50"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
 </wsDr>
@@ -637,7 +1429,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10026.44</v>
+        <v>10026.55</v>
       </c>
       <c r="C5" s="2">
         <f>B5-B4</f>
@@ -663,11 +1455,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B10"/>
+  <dimension ref="B1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="128" customWidth="1" min="2" max="2"/>
+    <col width="135" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -677,40 +1469,76 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
+          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Ga met de muis over een lijn om de waarde te zien. Zwarte lijn = koers, blauw = gemiddelde van 50 dagen, oranje = van 200 dagen, rode stippellijn = stop-loss (daar verkoopt de bot).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>1. Shell (SHELL.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="402" customHeight="1"/>
-    <row r="6" ht="30" customHeight="1"/>
-    <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>2. SAP (SAP.DE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="402" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1"/>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>3. Microsoft (MSFT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="402" customHeight="1"/>
-    <row r="12" ht="30" customHeight="1"/>
+          <t>1. Shell (SHELL.AS)  ·  46,46 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,73 zakt (-5,9%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>2. SAP (SAP.DE)  ·  196,94 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>3. Microsoft (MSFT)  ·  533,69 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -1633,4 +2461,4104 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Shell (SHELL.AS): Datum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Instap</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stop-loss (hier verkoopt de bot)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>SAP (SAP.DE): Datum</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Instap</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Stop-loss (hier verkoopt de bot)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT): Datum</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Instap</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Stop-loss (hier verkoopt de bot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>36.8773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.6114</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>137.64</v>
+      </c>
+      <c r="J2" t="n">
+        <v>144.8176</v>
+      </c>
+      <c r="L2" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M2" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>394.8866</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>401.1249</v>
+      </c>
+      <c r="S2" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T2" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>37.6594</v>
+      </c>
+      <c r="C3" t="n">
+        <v>35.6614</v>
+      </c>
+      <c r="E3" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F3" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="J3" t="n">
+        <v>144.652</v>
+      </c>
+      <c r="L3" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M3" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>400.3463</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>400.8928</v>
+      </c>
+      <c r="S3" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T3" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>37.5307</v>
+      </c>
+      <c r="C4" t="n">
+        <v>35.7021</v>
+      </c>
+      <c r="E4" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>138.26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>144.528</v>
+      </c>
+      <c r="L4" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M4" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>400.5601</v>
+      </c>
+      <c r="S4" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T4" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>37.8277</v>
+      </c>
+      <c r="C5" t="n">
+        <v>35.7452</v>
+      </c>
+      <c r="E5" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>136.42</v>
+      </c>
+      <c r="J5" t="n">
+        <v>144.4084</v>
+      </c>
+      <c r="L5" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M5" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>401.5341</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>400.345</v>
+      </c>
+      <c r="S5" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T5" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>38.2682</v>
+      </c>
+      <c r="C6" t="n">
+        <v>35.799</v>
+      </c>
+      <c r="D6" t="n">
+        <v>33.7968</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="J6" t="n">
+        <v>144.324</v>
+      </c>
+      <c r="K6" t="n">
+        <v>174.4005</v>
+      </c>
+      <c r="L6" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M6" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>397.0026</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>399.9036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>435.882</v>
+      </c>
+      <c r="S6" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T6" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>38.8028</v>
+      </c>
+      <c r="C7" t="n">
+        <v>35.863</v>
+      </c>
+      <c r="D7" t="n">
+        <v>33.8375</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>128.32</v>
+      </c>
+      <c r="J7" t="n">
+        <v>144.066</v>
+      </c>
+      <c r="K7" t="n">
+        <v>173.9035</v>
+      </c>
+      <c r="L7" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M7" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>389.6066</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>399.4268</v>
+      </c>
+      <c r="R7" t="n">
+        <v>435.2723</v>
+      </c>
+      <c r="S7" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T7" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>38.3871</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35.9135</v>
+      </c>
+      <c r="D8" t="n">
+        <v>33.8757</v>
+      </c>
+      <c r="E8" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>143.9888</v>
+      </c>
+      <c r="K8" t="n">
+        <v>173.4491</v>
+      </c>
+      <c r="L8" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M8" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>380.863</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>398.8242</v>
+      </c>
+      <c r="R8" t="n">
+        <v>434.611</v>
+      </c>
+      <c r="S8" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T8" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>37.9515</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35.931</v>
+      </c>
+      <c r="D9" t="n">
+        <v>33.9167</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>151.28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>144.0572</v>
+      </c>
+      <c r="K9" t="n">
+        <v>173.0393</v>
+      </c>
+      <c r="L9" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M9" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>380.9828</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>398.3214</v>
+      </c>
+      <c r="R9" t="n">
+        <v>433.8946</v>
+      </c>
+      <c r="S9" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T9" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>37.4713</v>
+      </c>
+      <c r="C10" t="n">
+        <v>35.9372</v>
+      </c>
+      <c r="D10" t="n">
+        <v>33.9548</v>
+      </c>
+      <c r="E10" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>159.24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>144.1076</v>
+      </c>
+      <c r="K10" t="n">
+        <v>172.6663</v>
+      </c>
+      <c r="L10" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M10" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>388.3689</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>398.0172</v>
+      </c>
+      <c r="R10" t="n">
+        <v>433.238</v>
+      </c>
+      <c r="S10" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T10" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>38.4415</v>
+      </c>
+      <c r="C11" t="n">
+        <v>35.9692</v>
+      </c>
+      <c r="D11" t="n">
+        <v>33.9987</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>162.04</v>
+      </c>
+      <c r="J11" t="n">
+        <v>144.28</v>
+      </c>
+      <c r="K11" t="n">
+        <v>172.343</v>
+      </c>
+      <c r="L11" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M11" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>392.6109</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>397.7139</v>
+      </c>
+      <c r="R11" t="n">
+        <v>432.5982</v>
+      </c>
+      <c r="S11" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T11" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>38.5108</v>
+      </c>
+      <c r="C12" t="n">
+        <v>35.9978</v>
+      </c>
+      <c r="D12" t="n">
+        <v>34.0424</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>155.92</v>
+      </c>
+      <c r="J12" t="n">
+        <v>144.3804</v>
+      </c>
+      <c r="K12" t="n">
+        <v>171.9849</v>
+      </c>
+      <c r="L12" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M12" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>389.8062</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>397.1057</v>
+      </c>
+      <c r="R12" t="n">
+        <v>431.9565</v>
+      </c>
+      <c r="S12" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T12" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>39.3226</v>
+      </c>
+      <c r="C13" t="n">
+        <v>36.0495</v>
+      </c>
+      <c r="D13" t="n">
+        <v>34.0907</v>
+      </c>
+      <c r="E13" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>157.68</v>
+      </c>
+      <c r="J13" t="n">
+        <v>144.4984</v>
+      </c>
+      <c r="K13" t="n">
+        <v>171.6292</v>
+      </c>
+      <c r="L13" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M13" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>450.2524</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>397.6741</v>
+      </c>
+      <c r="R13" t="n">
+        <v>431.6738</v>
+      </c>
+      <c r="S13" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T13" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>39.4067</v>
+      </c>
+      <c r="C14" t="n">
+        <v>36.1112</v>
+      </c>
+      <c r="D14" t="n">
+        <v>34.1393</v>
+      </c>
+      <c r="E14" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>164.64</v>
+      </c>
+      <c r="J14" t="n">
+        <v>144.7016</v>
+      </c>
+      <c r="K14" t="n">
+        <v>171.301</v>
+      </c>
+      <c r="L14" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M14" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>463.8468</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>398.6364</v>
+      </c>
+      <c r="R14" t="n">
+        <v>431.4438</v>
+      </c>
+      <c r="S14" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T14" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>38.486</v>
+      </c>
+      <c r="C15" t="n">
+        <v>36.1495</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34.1818</v>
+      </c>
+      <c r="E15" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>167.38</v>
+      </c>
+      <c r="J15" t="n">
+        <v>145.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>170.9913</v>
+      </c>
+      <c r="L15" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M15" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>486.7337</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>399.9838</v>
+      </c>
+      <c r="R15" t="n">
+        <v>431.3306</v>
+      </c>
+      <c r="S15" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T15" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>38.0307</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36.1966</v>
+      </c>
+      <c r="D16" t="n">
+        <v>34.2215</v>
+      </c>
+      <c r="E16" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>169.26</v>
+      </c>
+      <c r="J16" t="n">
+        <v>145.4052</v>
+      </c>
+      <c r="K16" t="n">
+        <v>170.7022</v>
+      </c>
+      <c r="L16" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M16" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>491.884</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>401.4555</v>
+      </c>
+      <c r="R16" t="n">
+        <v>431.2438</v>
+      </c>
+      <c r="S16" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T16" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>38.392</v>
+      </c>
+      <c r="C17" t="n">
+        <v>36.2474</v>
+      </c>
+      <c r="D17" t="n">
+        <v>34.2607</v>
+      </c>
+      <c r="E17" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="J17" t="n">
+        <v>145.7928</v>
+      </c>
+      <c r="K17" t="n">
+        <v>170.384</v>
+      </c>
+      <c r="L17" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M17" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>486.5441</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>402.8307</v>
+      </c>
+      <c r="R17" t="n">
+        <v>431.1393</v>
+      </c>
+      <c r="S17" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T17" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>38.0059</v>
+      </c>
+      <c r="C18" t="n">
+        <v>36.2952</v>
+      </c>
+      <c r="D18" t="n">
+        <v>34.294</v>
+      </c>
+      <c r="E18" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>177.96</v>
+      </c>
+      <c r="J18" t="n">
+        <v>146.2468</v>
+      </c>
+      <c r="K18" t="n">
+        <v>170.0918</v>
+      </c>
+      <c r="L18" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M18" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>498.9207</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>404.5041</v>
+      </c>
+      <c r="R18" t="n">
+        <v>431.087</v>
+      </c>
+      <c r="S18" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T18" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>38.4019</v>
+      </c>
+      <c r="C19" t="n">
+        <v>36.3315</v>
+      </c>
+      <c r="D19" t="n">
+        <v>34.3294</v>
+      </c>
+      <c r="E19" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>146.4748</v>
+      </c>
+      <c r="K19" t="n">
+        <v>169.8238</v>
+      </c>
+      <c r="L19" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M19" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>499.0505</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>406.2472</v>
+      </c>
+      <c r="R19" t="n">
+        <v>431.0194</v>
+      </c>
+      <c r="S19" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T19" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>38.9662</v>
+      </c>
+      <c r="C20" t="n">
+        <v>36.374</v>
+      </c>
+      <c r="D20" t="n">
+        <v>34.3685</v>
+      </c>
+      <c r="E20" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F20" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>146.8316</v>
+      </c>
+      <c r="K20" t="n">
+        <v>169.5375</v>
+      </c>
+      <c r="L20" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M20" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>505.1091</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>407.8257</v>
+      </c>
+      <c r="R20" t="n">
+        <v>430.9778</v>
+      </c>
+      <c r="S20" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T20" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>38.6494</v>
+      </c>
+      <c r="C21" t="n">
+        <v>36.3981</v>
+      </c>
+      <c r="D21" t="n">
+        <v>34.4068</v>
+      </c>
+      <c r="E21" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F21" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>175.96</v>
+      </c>
+      <c r="J21" t="n">
+        <v>147.232</v>
+      </c>
+      <c r="K21" t="n">
+        <v>169.2701</v>
+      </c>
+      <c r="L21" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M21" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>502.8633</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>408.895</v>
+      </c>
+      <c r="R21" t="n">
+        <v>430.9106</v>
+      </c>
+      <c r="S21" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T21" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>38.605</v>
+      </c>
+      <c r="C22" t="n">
+        <v>36.4313</v>
+      </c>
+      <c r="D22" t="n">
+        <v>34.4429</v>
+      </c>
+      <c r="E22" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F22" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>175.38</v>
+      </c>
+      <c r="J22" t="n">
+        <v>147.4496</v>
+      </c>
+      <c r="K22" t="n">
+        <v>168.9889</v>
+      </c>
+      <c r="L22" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M22" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>491.5047</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>409.532</v>
+      </c>
+      <c r="R22" t="n">
+        <v>430.7866</v>
+      </c>
+      <c r="S22" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T22" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="C23" t="n">
+        <v>36.4703</v>
+      </c>
+      <c r="D23" t="n">
+        <v>34.4805</v>
+      </c>
+      <c r="E23" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F23" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>180.14</v>
+      </c>
+      <c r="J23" t="n">
+        <v>147.8228</v>
+      </c>
+      <c r="K23" t="n">
+        <v>168.7386</v>
+      </c>
+      <c r="L23" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M23" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>495.9464</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>410.6414</v>
+      </c>
+      <c r="R23" t="n">
+        <v>430.6696</v>
+      </c>
+      <c r="S23" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T23" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="C24" t="n">
+        <v>36.5118</v>
+      </c>
+      <c r="D24" t="n">
+        <v>34.5207</v>
+      </c>
+      <c r="E24" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>179.58</v>
+      </c>
+      <c r="J24" t="n">
+        <v>148.2524</v>
+      </c>
+      <c r="K24" t="n">
+        <v>168.5337</v>
+      </c>
+      <c r="L24" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M24" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>494.4691</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>412</v>
+      </c>
+      <c r="R24" t="n">
+        <v>430.5061</v>
+      </c>
+      <c r="S24" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T24" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>39.785</v>
+      </c>
+      <c r="C25" t="n">
+        <v>36.5781</v>
+      </c>
+      <c r="D25" t="n">
+        <v>34.5641</v>
+      </c>
+      <c r="E25" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F25" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>148.8084</v>
+      </c>
+      <c r="K25" t="n">
+        <v>168.3358</v>
+      </c>
+      <c r="L25" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M25" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>479.4474</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>413.044</v>
+      </c>
+      <c r="R25" t="n">
+        <v>430.2151</v>
+      </c>
+      <c r="S25" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T25" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="C26" t="n">
+        <v>36.6336</v>
+      </c>
+      <c r="D26" t="n">
+        <v>34.6092</v>
+      </c>
+      <c r="E26" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F26" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>149.5324</v>
+      </c>
+      <c r="K26" t="n">
+        <v>168.1618</v>
+      </c>
+      <c r="L26" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M26" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>480.725</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>414.3408</v>
+      </c>
+      <c r="R26" t="n">
+        <v>429.933</v>
+      </c>
+      <c r="S26" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T26" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="C27" t="n">
+        <v>36.6884</v>
+      </c>
+      <c r="D27" t="n">
+        <v>34.6545</v>
+      </c>
+      <c r="E27" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F27" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>185.64</v>
+      </c>
+      <c r="J27" t="n">
+        <v>150.4472</v>
+      </c>
+      <c r="K27" t="n">
+        <v>167.9648</v>
+      </c>
+      <c r="L27" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M27" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>483.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>415.7895</v>
+      </c>
+      <c r="R27" t="n">
+        <v>429.7427</v>
+      </c>
+      <c r="S27" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T27" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="C28" t="n">
+        <v>36.7478</v>
+      </c>
+      <c r="D28" t="n">
+        <v>34.6988</v>
+      </c>
+      <c r="E28" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>188.12</v>
+      </c>
+      <c r="J28" t="n">
+        <v>151.4044</v>
+      </c>
+      <c r="K28" t="n">
+        <v>167.794</v>
+      </c>
+      <c r="L28" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M28" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>481.15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>417.3594</v>
+      </c>
+      <c r="R28" t="n">
+        <v>429.5805</v>
+      </c>
+      <c r="S28" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T28" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>39.775</v>
+      </c>
+      <c r="C29" t="n">
+        <v>36.8369</v>
+      </c>
+      <c r="D29" t="n">
+        <v>34.7421</v>
+      </c>
+      <c r="E29" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F29" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>152.2848</v>
+      </c>
+      <c r="K29" t="n">
+        <v>167.6093</v>
+      </c>
+      <c r="L29" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M29" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>483.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>419.092</v>
+      </c>
+      <c r="R29" t="n">
+        <v>429.4327</v>
+      </c>
+      <c r="S29" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T29" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>36.926</v>
+      </c>
+      <c r="D30" t="n">
+        <v>34.783</v>
+      </c>
+      <c r="E30" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>185.46</v>
+      </c>
+      <c r="J30" t="n">
+        <v>153.136</v>
+      </c>
+      <c r="K30" t="n">
+        <v>167.4651</v>
+      </c>
+      <c r="L30" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M30" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>487.31</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>421.046</v>
+      </c>
+      <c r="R30" t="n">
+        <v>429.3185</v>
+      </c>
+      <c r="S30" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T30" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="C31" t="n">
+        <v>37.0192</v>
+      </c>
+      <c r="D31" t="n">
+        <v>34.8202</v>
+      </c>
+      <c r="E31" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F31" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="J31" t="n">
+        <v>153.9128</v>
+      </c>
+      <c r="K31" t="n">
+        <v>167.3049</v>
+      </c>
+      <c r="L31" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M31" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>491.71</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>423.0801</v>
+      </c>
+      <c r="R31" t="n">
+        <v>429.262</v>
+      </c>
+      <c r="S31" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T31" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="C32" t="n">
+        <v>37.117</v>
+      </c>
+      <c r="D32" t="n">
+        <v>34.8559</v>
+      </c>
+      <c r="E32" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F32" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>189.88</v>
+      </c>
+      <c r="J32" t="n">
+        <v>155.0132</v>
+      </c>
+      <c r="K32" t="n">
+        <v>167.1911</v>
+      </c>
+      <c r="L32" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M32" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>496.37</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>425.0273</v>
+      </c>
+      <c r="R32" t="n">
+        <v>429.2786</v>
+      </c>
+      <c r="S32" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T32" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>39.145</v>
+      </c>
+      <c r="C33" t="n">
+        <v>37.2162</v>
+      </c>
+      <c r="D33" t="n">
+        <v>34.8941</v>
+      </c>
+      <c r="E33" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F33" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>191.32</v>
+      </c>
+      <c r="J33" t="n">
+        <v>156.1568</v>
+      </c>
+      <c r="K33" t="n">
+        <v>167.0806</v>
+      </c>
+      <c r="L33" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M33" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>505.06</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>427.2667</v>
+      </c>
+      <c r="R33" t="n">
+        <v>429.3401</v>
+      </c>
+      <c r="S33" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T33" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>39.335</v>
+      </c>
+      <c r="C34" t="n">
+        <v>37.3111</v>
+      </c>
+      <c r="D34" t="n">
+        <v>34.9333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F34" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>157.3304</v>
+      </c>
+      <c r="K34" t="n">
+        <v>166.9613</v>
+      </c>
+      <c r="L34" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M34" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>513.53</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>429.9734</v>
+      </c>
+      <c r="R34" t="n">
+        <v>429.3984</v>
+      </c>
+      <c r="S34" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T34" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>40.155</v>
+      </c>
+      <c r="C35" t="n">
+        <v>37.4239</v>
+      </c>
+      <c r="D35" t="n">
+        <v>34.9763</v>
+      </c>
+      <c r="E35" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>184.26</v>
+      </c>
+      <c r="J35" t="n">
+        <v>158.3252</v>
+      </c>
+      <c r="K35" t="n">
+        <v>166.8103</v>
+      </c>
+      <c r="L35" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M35" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>507.29</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>432.5454</v>
+      </c>
+      <c r="R35" t="n">
+        <v>429.4122</v>
+      </c>
+      <c r="S35" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T35" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="C36" t="n">
+        <v>37.5499</v>
+      </c>
+      <c r="D36" t="n">
+        <v>35.0217</v>
+      </c>
+      <c r="E36" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>181.44</v>
+      </c>
+      <c r="J36" t="n">
+        <v>159.2568</v>
+      </c>
+      <c r="K36" t="n">
+        <v>166.6796</v>
+      </c>
+      <c r="L36" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M36" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>501.02</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>435.2328</v>
+      </c>
+      <c r="R36" t="n">
+        <v>429.3825</v>
+      </c>
+      <c r="S36" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T36" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="C37" t="n">
+        <v>37.6767</v>
+      </c>
+      <c r="D37" t="n">
+        <v>35.0679</v>
+      </c>
+      <c r="E37" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F37" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>185.58</v>
+      </c>
+      <c r="J37" t="n">
+        <v>160.3228</v>
+      </c>
+      <c r="K37" t="n">
+        <v>166.5898</v>
+      </c>
+      <c r="L37" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M37" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>496.82</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>437.7045</v>
+      </c>
+      <c r="R37" t="n">
+        <v>429.3706</v>
+      </c>
+      <c r="S37" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T37" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>40.105</v>
+      </c>
+      <c r="C38" t="n">
+        <v>37.8115</v>
+      </c>
+      <c r="D38" t="n">
+        <v>35.113</v>
+      </c>
+      <c r="E38" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F38" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>185.68</v>
+      </c>
+      <c r="J38" t="n">
+        <v>161.3336</v>
+      </c>
+      <c r="K38" t="n">
+        <v>166.5086</v>
+      </c>
+      <c r="L38" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M38" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>510.12</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>440.6114</v>
+      </c>
+      <c r="R38" t="n">
+        <v>429.3912</v>
+      </c>
+      <c r="S38" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T38" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="C39" t="n">
+        <v>37.9551</v>
+      </c>
+      <c r="D39" t="n">
+        <v>35.1619</v>
+      </c>
+      <c r="E39" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F39" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>162.2568</v>
+      </c>
+      <c r="K39" t="n">
+        <v>166.4122</v>
+      </c>
+      <c r="L39" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M39" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>443.5621</v>
+      </c>
+      <c r="R39" t="n">
+        <v>429.3729</v>
+      </c>
+      <c r="S39" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T39" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>40.855</v>
+      </c>
+      <c r="C40" t="n">
+        <v>38.0977</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35.2131</v>
+      </c>
+      <c r="E40" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F40" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>163.2108</v>
+      </c>
+      <c r="K40" t="n">
+        <v>166.3049</v>
+      </c>
+      <c r="L40" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M40" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>493.95</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>445.9957</v>
+      </c>
+      <c r="R40" t="n">
+        <v>429.3939</v>
+      </c>
+      <c r="S40" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T40" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="C41" t="n">
+        <v>38.2513</v>
+      </c>
+      <c r="D41" t="n">
+        <v>35.2646</v>
+      </c>
+      <c r="E41" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F41" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>182.86</v>
+      </c>
+      <c r="J41" t="n">
+        <v>164.0504</v>
+      </c>
+      <c r="K41" t="n">
+        <v>166.2113</v>
+      </c>
+      <c r="L41" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M41" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>491.65</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>448.4712</v>
+      </c>
+      <c r="R41" t="n">
+        <v>429.4364</v>
+      </c>
+      <c r="S41" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T41" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="C42" t="n">
+        <v>38.4034</v>
+      </c>
+      <c r="D42" t="n">
+        <v>35.3174</v>
+      </c>
+      <c r="E42" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F42" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>177.82</v>
+      </c>
+      <c r="J42" t="n">
+        <v>164.7724</v>
+      </c>
+      <c r="K42" t="n">
+        <v>166.0803</v>
+      </c>
+      <c r="L42" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M42" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>492.44</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>450.8736</v>
+      </c>
+      <c r="R42" t="n">
+        <v>429.5215</v>
+      </c>
+      <c r="S42" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T42" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>41.415</v>
+      </c>
+      <c r="C43" t="n">
+        <v>38.5608</v>
+      </c>
+      <c r="D43" t="n">
+        <v>35.3717</v>
+      </c>
+      <c r="E43" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F43" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="J43" t="n">
+        <v>165.5248</v>
+      </c>
+      <c r="K43" t="n">
+        <v>165.9594</v>
+      </c>
+      <c r="L43" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M43" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>495.63</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>453.115</v>
+      </c>
+      <c r="R43" t="n">
+        <v>429.654</v>
+      </c>
+      <c r="S43" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T43" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="C44" t="n">
+        <v>38.7226</v>
+      </c>
+      <c r="D44" t="n">
+        <v>35.4269</v>
+      </c>
+      <c r="E44" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F44" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>186.26</v>
+      </c>
+      <c r="J44" t="n">
+        <v>166.4488</v>
+      </c>
+      <c r="K44" t="n">
+        <v>165.8745</v>
+      </c>
+      <c r="L44" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M44" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>505.41</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>455.4281</v>
+      </c>
+      <c r="R44" t="n">
+        <v>429.8259</v>
+      </c>
+      <c r="S44" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T44" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="C45" t="n">
+        <v>38.8782</v>
+      </c>
+      <c r="D45" t="n">
+        <v>35.4854</v>
+      </c>
+      <c r="E45" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F45" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>187.08</v>
+      </c>
+      <c r="J45" t="n">
+        <v>167.3124</v>
+      </c>
+      <c r="K45" t="n">
+        <v>165.7921</v>
+      </c>
+      <c r="L45" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M45" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>497.12</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>457.6502</v>
+      </c>
+      <c r="R45" t="n">
+        <v>429.9416</v>
+      </c>
+      <c r="S45" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T45" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>41.825</v>
+      </c>
+      <c r="C46" t="n">
+        <v>38.9989</v>
+      </c>
+      <c r="D46" t="n">
+        <v>35.5403</v>
+      </c>
+      <c r="E46" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F46" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>186.56</v>
+      </c>
+      <c r="J46" t="n">
+        <v>168.2844</v>
+      </c>
+      <c r="K46" t="n">
+        <v>165.6996</v>
+      </c>
+      <c r="L46" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M46" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>490.3</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>459.694</v>
+      </c>
+      <c r="R46" t="n">
+        <v>429.9809</v>
+      </c>
+      <c r="S46" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T46" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="C47" t="n">
+        <v>39.1225</v>
+      </c>
+      <c r="D47" t="n">
+        <v>35.5926</v>
+      </c>
+      <c r="E47" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F47" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>188</v>
+      </c>
+      <c r="J47" t="n">
+        <v>169.2896</v>
+      </c>
+      <c r="K47" t="n">
+        <v>165.6125</v>
+      </c>
+      <c r="L47" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M47" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>497.75</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>461.9966</v>
+      </c>
+      <c r="R47" t="n">
+        <v>430.0251</v>
+      </c>
+      <c r="S47" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T47" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>41.315</v>
+      </c>
+      <c r="C48" t="n">
+        <v>39.2414</v>
+      </c>
+      <c r="D48" t="n">
+        <v>35.6436</v>
+      </c>
+      <c r="E48" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F48" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="J48" t="n">
+        <v>170.2004</v>
+      </c>
+      <c r="K48" t="n">
+        <v>165.5062</v>
+      </c>
+      <c r="L48" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M48" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>493.78</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>464.1995</v>
+      </c>
+      <c r="R48" t="n">
+        <v>430.0757</v>
+      </c>
+      <c r="S48" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T48" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>40.775</v>
+      </c>
+      <c r="C49" t="n">
+        <v>39.3341</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35.6939</v>
+      </c>
+      <c r="E49" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F49" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>182.86</v>
+      </c>
+      <c r="J49" t="n">
+        <v>171.0432</v>
+      </c>
+      <c r="K49" t="n">
+        <v>165.4052</v>
+      </c>
+      <c r="L49" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M49" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>501.61</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>466.5442</v>
+      </c>
+      <c r="R49" t="n">
+        <v>430.1492</v>
+      </c>
+      <c r="S49" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T49" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="C50" t="n">
+        <v>39.4244</v>
+      </c>
+      <c r="D50" t="n">
+        <v>35.746</v>
+      </c>
+      <c r="E50" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F50" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>182.32</v>
+      </c>
+      <c r="J50" t="n">
+        <v>171.9552</v>
+      </c>
+      <c r="K50" t="n">
+        <v>165.2836</v>
+      </c>
+      <c r="L50" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M50" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>498</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>468.699</v>
+      </c>
+      <c r="R50" t="n">
+        <v>430.2656</v>
+      </c>
+      <c r="S50" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T50" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="C51" t="n">
+        <v>39.5272</v>
+      </c>
+      <c r="D51" t="n">
+        <v>35.8024</v>
+      </c>
+      <c r="E51" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F51" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>186.46</v>
+      </c>
+      <c r="J51" t="n">
+        <v>172.9448</v>
+      </c>
+      <c r="K51" t="n">
+        <v>165.1675</v>
+      </c>
+      <c r="L51" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M51" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>500.59</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>471.0267</v>
+      </c>
+      <c r="R51" t="n">
+        <v>430.3795</v>
+      </c>
+      <c r="S51" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T51" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="C52" t="n">
+        <v>39.6382</v>
+      </c>
+      <c r="D52" t="n">
+        <v>35.8638</v>
+      </c>
+      <c r="E52" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F52" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="J52" t="n">
+        <v>173.8756</v>
+      </c>
+      <c r="K52" t="n">
+        <v>165.0554</v>
+      </c>
+      <c r="L52" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M52" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>497.93</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>473.0876</v>
+      </c>
+      <c r="R52" t="n">
+        <v>430.4686</v>
+      </c>
+      <c r="S52" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T52" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="C53" t="n">
+        <v>39.7263</v>
+      </c>
+      <c r="D53" t="n">
+        <v>35.9239</v>
+      </c>
+      <c r="E53" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F53" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="J53" t="n">
+        <v>174.8356</v>
+      </c>
+      <c r="K53" t="n">
+        <v>164.9525</v>
+      </c>
+      <c r="L53" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M53" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>516.17</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>475.4041</v>
+      </c>
+      <c r="R53" t="n">
+        <v>430.6098</v>
+      </c>
+      <c r="S53" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T53" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>42.725</v>
+      </c>
+      <c r="C54" t="n">
+        <v>39.8301</v>
+      </c>
+      <c r="D54" t="n">
+        <v>35.9888</v>
+      </c>
+      <c r="E54" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F54" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>184.02</v>
+      </c>
+      <c r="J54" t="n">
+        <v>175.7508</v>
+      </c>
+      <c r="K54" t="n">
+        <v>164.8355</v>
+      </c>
+      <c r="L54" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M54" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>509.22</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>477.7269</v>
+      </c>
+      <c r="R54" t="n">
+        <v>430.7113</v>
+      </c>
+      <c r="S54" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T54" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="C55" t="n">
+        <v>39.9146</v>
+      </c>
+      <c r="D55" t="n">
+        <v>36.0498</v>
+      </c>
+      <c r="E55" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F55" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>185.32</v>
+      </c>
+      <c r="J55" t="n">
+        <v>176.7288</v>
+      </c>
+      <c r="K55" t="n">
+        <v>164.733</v>
+      </c>
+      <c r="L55" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M55" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>508.96</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>479.8754</v>
+      </c>
+      <c r="R55" t="n">
+        <v>430.8784</v>
+      </c>
+      <c r="S55" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T55" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="C56" t="n">
+        <v>39.9874</v>
+      </c>
+      <c r="D56" t="n">
+        <v>36.1135</v>
+      </c>
+      <c r="E56" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F56" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>185.66</v>
+      </c>
+      <c r="J56" t="n">
+        <v>177.8012</v>
+      </c>
+      <c r="K56" t="n">
+        <v>164.6377</v>
+      </c>
+      <c r="L56" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M56" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>482.1933</v>
+      </c>
+      <c r="R56" t="n">
+        <v>431.0408</v>
+      </c>
+      <c r="S56" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T56" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="C57" t="n">
+        <v>40.0562</v>
+      </c>
+      <c r="D57" t="n">
+        <v>36.1777</v>
+      </c>
+      <c r="E57" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F57" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>186.74</v>
+      </c>
+      <c r="J57" t="n">
+        <v>178.9696</v>
+      </c>
+      <c r="K57" t="n">
+        <v>164.5407</v>
+      </c>
+      <c r="L57" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M57" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>512.8</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>484.6572</v>
+      </c>
+      <c r="R57" t="n">
+        <v>431.2272</v>
+      </c>
+      <c r="S57" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T57" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>40.1364</v>
+      </c>
+      <c r="D58" t="n">
+        <v>36.2422</v>
+      </c>
+      <c r="E58" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F58" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>183.92</v>
+      </c>
+      <c r="J58" t="n">
+        <v>179.844</v>
+      </c>
+      <c r="K58" t="n">
+        <v>164.4442</v>
+      </c>
+      <c r="L58" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M58" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>517.53</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>487.3905</v>
+      </c>
+      <c r="R58" t="n">
+        <v>431.4557</v>
+      </c>
+      <c r="S58" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T58" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>42.865</v>
+      </c>
+      <c r="C59" t="n">
+        <v>40.2347</v>
+      </c>
+      <c r="D59" t="n">
+        <v>36.3069</v>
+      </c>
+      <c r="E59" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F59" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="J59" t="n">
+        <v>180.5192</v>
+      </c>
+      <c r="K59" t="n">
+        <v>164.3515</v>
+      </c>
+      <c r="L59" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M59" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>525.1799999999999</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>490.2745</v>
+      </c>
+      <c r="R59" t="n">
+        <v>431.7147</v>
+      </c>
+      <c r="S59" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T59" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>43.185</v>
+      </c>
+      <c r="C60" t="n">
+        <v>40.349</v>
+      </c>
+      <c r="D60" t="n">
+        <v>36.3726</v>
+      </c>
+      <c r="E60" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F60" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>181.1064</v>
+      </c>
+      <c r="K60" t="n">
+        <v>164.2647</v>
+      </c>
+      <c r="L60" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M60" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>529.3</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>493.0931</v>
+      </c>
+      <c r="R60" t="n">
+        <v>431.9956</v>
+      </c>
+      <c r="S60" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T60" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="C61" t="n">
+        <v>40.4451</v>
+      </c>
+      <c r="D61" t="n">
+        <v>36.4388</v>
+      </c>
+      <c r="E61" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F61" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>187.62</v>
+      </c>
+      <c r="J61" t="n">
+        <v>181.618</v>
+      </c>
+      <c r="K61" t="n">
+        <v>164.1762</v>
+      </c>
+      <c r="L61" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M61" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>529.76</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>495.8361</v>
+      </c>
+      <c r="R61" t="n">
+        <v>432.2398</v>
+      </c>
+      <c r="S61" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T61" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="C62" t="n">
+        <v>40.5699</v>
+      </c>
+      <c r="D62" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="E62" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F62" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>184.62</v>
+      </c>
+      <c r="J62" t="n">
+        <v>182.192</v>
+      </c>
+      <c r="K62" t="n">
+        <v>164.074</v>
+      </c>
+      <c r="L62" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M62" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>522.61</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>498.4921</v>
+      </c>
+      <c r="R62" t="n">
+        <v>432.4385</v>
+      </c>
+      <c r="S62" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T62" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>45.035</v>
+      </c>
+      <c r="C63" t="n">
+        <v>40.6842</v>
+      </c>
+      <c r="D63" t="n">
+        <v>36.5866</v>
+      </c>
+      <c r="E63" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F63" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>191.46</v>
+      </c>
+      <c r="J63" t="n">
+        <v>182.8676</v>
+      </c>
+      <c r="K63" t="n">
+        <v>164.0101</v>
+      </c>
+      <c r="L63" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M63" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>535.0700000000001</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>500.1885</v>
+      </c>
+      <c r="R63" t="n">
+        <v>432.7046</v>
+      </c>
+      <c r="S63" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T63" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="C64" t="n">
+        <v>40.8072</v>
+      </c>
+      <c r="D64" t="n">
+        <v>36.6625</v>
+      </c>
+      <c r="E64" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F64" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>194.46</v>
+      </c>
+      <c r="J64" t="n">
+        <v>183.464</v>
+      </c>
+      <c r="K64" t="n">
+        <v>163.9576</v>
+      </c>
+      <c r="L64" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M64" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>541.15</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>501.7346</v>
+      </c>
+      <c r="R64" t="n">
+        <v>432.9914</v>
+      </c>
+      <c r="S64" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T64" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="C65" t="n">
+        <v>40.9565</v>
+      </c>
+      <c r="D65" t="n">
+        <v>36.7398</v>
+      </c>
+      <c r="E65" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F65" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>197.28</v>
+      </c>
+      <c r="J65" t="n">
+        <v>184.062</v>
+      </c>
+      <c r="K65" t="n">
+        <v>163.9196</v>
+      </c>
+      <c r="L65" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M65" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>543.45</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>502.8689</v>
+      </c>
+      <c r="R65" t="n">
+        <v>433.2839</v>
+      </c>
+      <c r="S65" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T65" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>46.455</v>
+      </c>
+      <c r="C66" t="n">
+        <v>41.125</v>
+      </c>
+      <c r="D66" t="n">
+        <v>36.8183</v>
+      </c>
+      <c r="E66" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="F66" t="n">
+        <v>43.73250225612095</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>196.94</v>
+      </c>
+      <c r="J66" t="n">
+        <v>184.6156</v>
+      </c>
+      <c r="K66" t="n">
+        <v>163.9114</v>
+      </c>
+      <c r="L66" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="M66" t="n">
+        <v>181.0371344430106</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>533.6900000000001</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>503.705</v>
+      </c>
+      <c r="R66" t="n">
+        <v>433.5292</v>
+      </c>
+      <c r="S66" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="T66" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -189,8 +189,7 @@
           <h val="0.8"/>
         </manualLayout>
       </layout>
-      <lineChart>
-        <grouping val="standard"/>
+      <stockChart>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -200,10 +199,8 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
-              <a:solidFill>
-                <a:srgbClr val="0B0B0B"/>
-              </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -225,7 +222,6 @@
               <f>'Grafiekdata'!$B$2:$B$66</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
@@ -233,6 +229,216 @@
           <tx>
             <strRef>
               <f>'Grafiekdata'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$C$2:$C$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$D$2:$D$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$E$2:$E$66</f>
+              <numCache>
+                <pt idx="0"/>
+                <pt idx="1"/>
+                <pt idx="2"/>
+                <pt idx="3"/>
+                <pt idx="4"/>
+                <pt idx="5"/>
+                <pt idx="6"/>
+                <pt idx="7"/>
+                <pt idx="8"/>
+                <pt idx="9"/>
+                <pt idx="10"/>
+                <pt idx="11"/>
+                <pt idx="12"/>
+                <pt idx="13"/>
+                <pt idx="14"/>
+                <pt idx="15"/>
+                <pt idx="16"/>
+                <pt idx="17"/>
+                <pt idx="18"/>
+                <pt idx="19"/>
+                <pt idx="20"/>
+                <pt idx="21"/>
+                <pt idx="22"/>
+                <pt idx="23"/>
+                <pt idx="24"/>
+                <pt idx="25"/>
+                <pt idx="26"/>
+                <pt idx="27"/>
+                <pt idx="28"/>
+                <pt idx="29"/>
+                <pt idx="30"/>
+                <pt idx="31"/>
+                <pt idx="32"/>
+                <pt idx="33"/>
+                <pt idx="34"/>
+                <pt idx="35"/>
+                <pt idx="36"/>
+                <pt idx="37"/>
+                <pt idx="38"/>
+                <pt idx="39"/>
+                <pt idx="40"/>
+                <pt idx="41"/>
+                <pt idx="42"/>
+                <pt idx="43"/>
+                <pt idx="44"/>
+                <pt idx="45"/>
+                <pt idx="46"/>
+                <pt idx="47"/>
+                <pt idx="48"/>
+                <pt idx="49"/>
+                <pt idx="50"/>
+                <pt idx="51"/>
+                <pt idx="52"/>
+                <pt idx="53"/>
+                <pt idx="54"/>
+                <pt idx="55"/>
+                <pt idx="56"/>
+                <pt idx="57"/>
+                <pt idx="58"/>
+                <pt idx="59"/>
+                <pt idx="60"/>
+                <pt idx="61"/>
+                <pt idx="62"/>
+                <pt idx="63"/>
+                <pt idx="64"/>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <hiLowLines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </hiLowLines>
+        <upDownBars>
+          <gapWidth val="60"/>
+          <upBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="008300"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </upBars>
+          <downBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="E34948"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </downBars>
+        </upDownBars>
+        <axId val="10"/>
+        <axId val="100"/>
+      </stockChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -258,17 +464,17 @@
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$C$2:$C$66</f>
+              <f>'Grafiekdata'!$F$2:$F$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!D1</f>
+              <f>'Grafiekdata'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -294,17 +500,17 @@
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$D$2:$D$66</f>
+              <f>'Grafiekdata'!$G$2:$G$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!E1</f>
+              <f>'Grafiekdata'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -330,17 +536,17 @@
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$E$2:$E$66</f>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="7"/>
+          <order val="7"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!F1</f>
+              <f>'Grafiekdata'!I1</f>
             </strRef>
           </tx>
           <spPr>
@@ -366,7 +572,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$F$2:$F$66</f>
+              <f>'Grafiekdata'!$I$2:$I$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -430,9 +636,6 @@
         <majorUnit val="2.5"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -453,21 +656,18 @@
           <h val="0.8"/>
         </manualLayout>
       </layout>
-      <lineChart>
-        <grouping val="standard"/>
+      <stockChart>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!I1</f>
+              <f>'Grafiekdata'!L1</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
-              <a:solidFill>
-                <a:srgbClr val="0B0B0B"/>
-              </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -481,22 +681,231 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$H$2:$H$66</f>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$I$2:$I$66</f>
+              <f>'Grafiekdata'!$L$2:$L$66</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!J1</f>
+              <f>'Grafiekdata'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$M$2:$M$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$N$2:$N$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!O1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$O$2:$O$66</f>
+              <numCache>
+                <pt idx="0"/>
+                <pt idx="1"/>
+                <pt idx="2"/>
+                <pt idx="3"/>
+                <pt idx="4"/>
+                <pt idx="5"/>
+                <pt idx="6"/>
+                <pt idx="7"/>
+                <pt idx="8"/>
+                <pt idx="9"/>
+                <pt idx="10"/>
+                <pt idx="11"/>
+                <pt idx="12"/>
+                <pt idx="13"/>
+                <pt idx="14"/>
+                <pt idx="15"/>
+                <pt idx="16"/>
+                <pt idx="17"/>
+                <pt idx="18"/>
+                <pt idx="19"/>
+                <pt idx="20"/>
+                <pt idx="21"/>
+                <pt idx="22"/>
+                <pt idx="23"/>
+                <pt idx="24"/>
+                <pt idx="25"/>
+                <pt idx="26"/>
+                <pt idx="27"/>
+                <pt idx="28"/>
+                <pt idx="29"/>
+                <pt idx="30"/>
+                <pt idx="31"/>
+                <pt idx="32"/>
+                <pt idx="33"/>
+                <pt idx="34"/>
+                <pt idx="35"/>
+                <pt idx="36"/>
+                <pt idx="37"/>
+                <pt idx="38"/>
+                <pt idx="39"/>
+                <pt idx="40"/>
+                <pt idx="41"/>
+                <pt idx="42"/>
+                <pt idx="43"/>
+                <pt idx="44"/>
+                <pt idx="45"/>
+                <pt idx="46"/>
+                <pt idx="47"/>
+                <pt idx="48"/>
+                <pt idx="49"/>
+                <pt idx="50"/>
+                <pt idx="51"/>
+                <pt idx="52"/>
+                <pt idx="53"/>
+                <pt idx="54"/>
+                <pt idx="55"/>
+                <pt idx="56"/>
+                <pt idx="57"/>
+                <pt idx="58"/>
+                <pt idx="59"/>
+                <pt idx="60"/>
+                <pt idx="61"/>
+                <pt idx="62"/>
+                <pt idx="63"/>
+                <pt idx="64"/>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <hiLowLines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </hiLowLines>
+        <upDownBars>
+          <gapWidth val="60"/>
+          <upBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="008300"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </upBars>
+          <downBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="E34948"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </downBars>
+        </upDownBars>
+        <axId val="10"/>
+        <axId val="100"/>
+      </stockChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!P1</f>
             </strRef>
           </tx>
           <spPr>
@@ -517,22 +926,22 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$H$2:$H$66</f>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$J$2:$J$66</f>
+              <f>'Grafiekdata'!$P$2:$P$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!K1</f>
+              <f>'Grafiekdata'!Q1</f>
             </strRef>
           </tx>
           <spPr>
@@ -553,22 +962,22 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$H$2:$H$66</f>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$K$2:$K$66</f>
+              <f>'Grafiekdata'!$Q$2:$Q$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!L1</f>
+              <f>'Grafiekdata'!R1</f>
             </strRef>
           </tx>
           <spPr>
@@ -589,22 +998,22 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$H$2:$H$66</f>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$L$2:$L$66</f>
+              <f>'Grafiekdata'!$R$2:$R$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="7"/>
+          <order val="7"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!M1</f>
+              <f>'Grafiekdata'!S1</f>
             </strRef>
           </tx>
           <spPr>
@@ -625,12 +1034,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$H$2:$H$66</f>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$M$2:$M$66</f>
+              <f>'Grafiekdata'!$S$2:$S$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,9 +1103,6 @@
         <majorUnit val="20"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -717,21 +1123,18 @@
           <h val="0.8"/>
         </manualLayout>
       </layout>
-      <lineChart>
-        <grouping val="standard"/>
+      <stockChart>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!P1</f>
+              <f>'Grafiekdata'!V1</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
-              <a:solidFill>
-                <a:srgbClr val="0B0B0B"/>
-              </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -745,22 +1148,231 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$O$2:$O$66</f>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$P$2:$P$66</f>
+              <f>'Grafiekdata'!$V$2:$V$66</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!Q1</f>
+              <f>'Grafiekdata'!W1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$W$2:$W$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!X1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$X$2:$X$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!Y1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$Y$2:$Y$66</f>
+              <numCache>
+                <pt idx="0"/>
+                <pt idx="1"/>
+                <pt idx="2"/>
+                <pt idx="3"/>
+                <pt idx="4"/>
+                <pt idx="5"/>
+                <pt idx="6"/>
+                <pt idx="7"/>
+                <pt idx="8"/>
+                <pt idx="9"/>
+                <pt idx="10"/>
+                <pt idx="11"/>
+                <pt idx="12"/>
+                <pt idx="13"/>
+                <pt idx="14"/>
+                <pt idx="15"/>
+                <pt idx="16"/>
+                <pt idx="17"/>
+                <pt idx="18"/>
+                <pt idx="19"/>
+                <pt idx="20"/>
+                <pt idx="21"/>
+                <pt idx="22"/>
+                <pt idx="23"/>
+                <pt idx="24"/>
+                <pt idx="25"/>
+                <pt idx="26"/>
+                <pt idx="27"/>
+                <pt idx="28"/>
+                <pt idx="29"/>
+                <pt idx="30"/>
+                <pt idx="31"/>
+                <pt idx="32"/>
+                <pt idx="33"/>
+                <pt idx="34"/>
+                <pt idx="35"/>
+                <pt idx="36"/>
+                <pt idx="37"/>
+                <pt idx="38"/>
+                <pt idx="39"/>
+                <pt idx="40"/>
+                <pt idx="41"/>
+                <pt idx="42"/>
+                <pt idx="43"/>
+                <pt idx="44"/>
+                <pt idx="45"/>
+                <pt idx="46"/>
+                <pt idx="47"/>
+                <pt idx="48"/>
+                <pt idx="49"/>
+                <pt idx="50"/>
+                <pt idx="51"/>
+                <pt idx="52"/>
+                <pt idx="53"/>
+                <pt idx="54"/>
+                <pt idx="55"/>
+                <pt idx="56"/>
+                <pt idx="57"/>
+                <pt idx="58"/>
+                <pt idx="59"/>
+                <pt idx="60"/>
+                <pt idx="61"/>
+                <pt idx="62"/>
+                <pt idx="63"/>
+                <pt idx="64"/>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <hiLowLines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </hiLowLines>
+        <upDownBars>
+          <gapWidth val="60"/>
+          <upBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="008300"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </upBars>
+          <downBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="E34948"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </downBars>
+        </upDownBars>
+        <axId val="10"/>
+        <axId val="100"/>
+      </stockChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!Z1</f>
             </strRef>
           </tx>
           <spPr>
@@ -781,22 +1393,22 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$O$2:$O$66</f>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$Q$2:$Q$66</f>
+              <f>'Grafiekdata'!$Z$2:$Z$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!R1</f>
+              <f>'Grafiekdata'!AA1</f>
             </strRef>
           </tx>
           <spPr>
@@ -817,22 +1429,22 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$O$2:$O$66</f>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$R$2:$R$66</f>
+              <f>'Grafiekdata'!$AA$2:$AA$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!S1</f>
+              <f>'Grafiekdata'!AB1</f>
             </strRef>
           </tx>
           <spPr>
@@ -853,22 +1465,22 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$O$2:$O$66</f>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$S$2:$S$66</f>
+              <f>'Grafiekdata'!$AB$2:$AB$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="7"/>
+          <order val="7"/>
           <tx>
             <strRef>
-              <f>'Grafiekdata'!T1</f>
+              <f>'Grafiekdata'!AC1</f>
             </strRef>
           </tx>
           <spPr>
@@ -889,12 +1501,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Grafiekdata'!$O$2:$O$66</f>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Grafiekdata'!$T$2:$T$66</f>
+              <f>'Grafiekdata'!$AC$2:$AC$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -958,9 +1570,6 @@
         <majorUnit val="50"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -973,7 +1582,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="4140000"/>
@@ -995,7 +1604,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="4140000"/>
@@ -1017,7 +1626,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="4140000"/>
@@ -1455,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B64"/>
+  <dimension ref="B1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1469,10 +2078,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Ga met de muis over een lijn om de waarde te zien. Zwarte lijn = koers, blauw = gemiddelde van 50 dagen, oranje = van 200 dagen, rode stippellijn = stop-loss (daar verkoopt de bot).</t>
+          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke kaars is één handelsdag: groen = die dag gestegen, rood = die dag gedaald; de dunne streep is de hoogste en laagste koers. Blauwe lijn = gemiddelde van 50 dagen, oranje = van 200 dagen, grijze stippellijn = instap, rode stippellijn = stop-loss (daar verkoopt de bot). Ga met de muis over een kaars of lijn voor de waarde.</t>
         </is>
       </c>
     </row>
@@ -1497,45 +2106,333 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00008300"/>
+              <sz val="11"/>
+            </rPr>
+            <t>▮ groen</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gestegen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="11"/>
+            </rPr>
+            <t>▮ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gedaald   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002A78D6"/>
+              <sz val="11"/>
+            </rPr>
+            <t>━ blauw</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00EB6834"/>
+              <sz val="11"/>
+            </rPr>
+            <t>━ oranje</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>╌ grijs</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = instap   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="11"/>
+            </rPr>
+            <t>╌ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>2. SAP (SAP.DE)  ·  196,94 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="9" t="inlineStr">
         <is>
+          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
           <t>Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="B62" s="8" t="inlineStr">
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00008300"/>
+              <sz val="11"/>
+            </rPr>
+            <t>▮ groen</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gestegen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="11"/>
+            </rPr>
+            <t>▮ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gedaald   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002A78D6"/>
+              <sz val="11"/>
+            </rPr>
+            <t>━ blauw</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00EB6834"/>
+              <sz val="11"/>
+            </rPr>
+            <t>━ oranje</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>╌ grijs</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = instap   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="11"/>
+            </rPr>
+            <t>╌ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>3. Microsoft (MSFT)  ·  533,69 USD</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="9" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="9" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00008300"/>
+              <sz val="11"/>
+            </rPr>
+            <t>▮ groen</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gestegen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="11"/>
+            </rPr>
+            <t>▮ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gedaald   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002A78D6"/>
+              <sz val="11"/>
+            </rPr>
+            <t>━ blauw</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00EB6834"/>
+              <sz val="11"/>
+            </rPr>
+            <t>━ oranje</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>╌ grijs</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = instap   </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="11"/>
+            </rPr>
+            <t>╌ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2469,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2480,85 +3377,130 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Koers</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Hoogste</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Laagste</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>50-daags gemiddelde</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>200-daags gemiddelde</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Instap</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Stop-loss (hier verkoopt de bot)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>SAP (SAP.DE): Datum</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Koers</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Hoogste</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Laagste</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>50-daags gemiddelde</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>200-daags gemiddelde</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Instap</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Stop-loss (hier verkoopt de bot)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Microsoft (MSFT): Datum</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Koers</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Hoogste</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Laagste</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>50-daags gemiddelde</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>200-daags gemiddelde</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Instap</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Stop-loss (hier verkoopt de bot)</t>
         </is>
@@ -2571,49 +3513,76 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>36.5803</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.011</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.3724</v>
+      </c>
+      <c r="E2" t="n">
         <v>36.8773</v>
       </c>
-      <c r="C2" t="n">
+      <c r="F2" t="n">
         <v>35.6114</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>16 jul</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>138.24</v>
+      </c>
+      <c r="N2" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="O2" t="n">
         <v>137.64</v>
       </c>
-      <c r="J2" t="n">
+      <c r="P2" t="n">
         <v>144.8176</v>
       </c>
-      <c r="L2" t="n">
+      <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M2" t="n">
+      <c r="S2" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>15 jul</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="V2" t="n">
+        <v>387.0713</v>
+      </c>
+      <c r="W2" t="n">
+        <v>398.2104</v>
+      </c>
+      <c r="X2" t="n">
+        <v>385.674</v>
+      </c>
+      <c r="Y2" t="n">
         <v>394.8866</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Z2" t="n">
         <v>401.1249</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AB2" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AC2" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -2624,49 +3593,76 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>36.912</v>
+      </c>
+      <c r="C3" t="n">
+        <v>37.8871</v>
+      </c>
+      <c r="D3" t="n">
+        <v>36.912</v>
+      </c>
+      <c r="E3" t="n">
         <v>37.6594</v>
       </c>
-      <c r="C3" t="n">
+      <c r="F3" t="n">
         <v>35.6614</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>17 jul</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>141.54</v>
+      </c>
+      <c r="N3" t="n">
+        <v>137.32</v>
+      </c>
+      <c r="O3" t="n">
         <v>137.92</v>
       </c>
-      <c r="J3" t="n">
+      <c r="P3" t="n">
         <v>144.652</v>
       </c>
-      <c r="L3" t="n">
+      <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M3" t="n">
+      <c r="S3" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>16 jul</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="V3" t="n">
+        <v>397.5616</v>
+      </c>
+      <c r="W3" t="n">
+        <v>405.2271</v>
+      </c>
+      <c r="X3" t="n">
+        <v>391.3133</v>
+      </c>
+      <c r="Y3" t="n">
         <v>400.3463</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Z3" t="n">
         <v>400.8928</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AB3" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AC3" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -2677,49 +3673,76 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>38.0653</v>
+      </c>
+      <c r="C4" t="n">
+        <v>38.1742</v>
+      </c>
+      <c r="D4" t="n">
+        <v>37.1496</v>
+      </c>
+      <c r="E4" t="n">
         <v>37.5307</v>
       </c>
-      <c r="C4" t="n">
+      <c r="F4" t="n">
         <v>35.7021</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>20 jul</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
+        <v>138</v>
+      </c>
+      <c r="M4" t="n">
+        <v>140.04</v>
+      </c>
+      <c r="N4" t="n">
+        <v>134.98</v>
+      </c>
+      <c r="O4" t="n">
         <v>138.26</v>
       </c>
-      <c r="J4" t="n">
+      <c r="P4" t="n">
         <v>144.528</v>
       </c>
-      <c r="L4" t="n">
+      <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M4" t="n">
+      <c r="S4" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>17 jul</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="V4" t="n">
+        <v>394.118</v>
+      </c>
+      <c r="W4" t="n">
+        <v>397.6414</v>
+      </c>
+      <c r="X4" t="n">
+        <v>388.6583</v>
+      </c>
+      <c r="Y4" t="n">
         <v>393.08</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Z4" t="n">
         <v>400.5601</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AB4" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AC4" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -2730,49 +3753,76 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>37.5703</v>
+      </c>
+      <c r="C5" t="n">
         <v>37.8277</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
+        <v>37.4169</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37.8277</v>
+      </c>
+      <c r="F5" t="n">
         <v>35.7452</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>21 jul</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
+        <v>137.74</v>
+      </c>
+      <c r="M5" t="n">
+        <v>137.84</v>
+      </c>
+      <c r="N5" t="n">
+        <v>135.34</v>
+      </c>
+      <c r="O5" t="n">
         <v>136.42</v>
       </c>
-      <c r="J5" t="n">
+      <c r="P5" t="n">
         <v>144.4084</v>
       </c>
-      <c r="L5" t="n">
+      <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M5" t="n">
+      <c r="S5" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>20 jul</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="V5" t="n">
+        <v>390.6746</v>
+      </c>
+      <c r="W5" t="n">
+        <v>402.4224</v>
+      </c>
+      <c r="X5" t="n">
+        <v>388.9179</v>
+      </c>
+      <c r="Y5" t="n">
         <v>401.5341</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Z5" t="n">
         <v>400.345</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AB5" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AC5" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -2783,58 +3833,85 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>38.095</v>
+      </c>
+      <c r="C6" t="n">
+        <v>38.6098</v>
+      </c>
+      <c r="D6" t="n">
+        <v>37.9267</v>
+      </c>
+      <c r="E6" t="n">
         <v>38.2682</v>
       </c>
-      <c r="C6" t="n">
+      <c r="F6" t="n">
         <v>35.799</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>33.7968</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>22 jul</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>136.02</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="N6" t="n">
         <v>132.04</v>
       </c>
-      <c r="J6" t="n">
+      <c r="O6" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="P6" t="n">
         <v>144.324</v>
       </c>
-      <c r="K6" t="n">
+      <c r="Q6" t="n">
         <v>174.4005</v>
       </c>
-      <c r="L6" t="n">
+      <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M6" t="n">
+      <c r="S6" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>21 jul</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="V6" t="n">
+        <v>398.0606</v>
+      </c>
+      <c r="W6" t="n">
+        <v>400.7156</v>
+      </c>
+      <c r="X6" t="n">
+        <v>395.5753</v>
+      </c>
+      <c r="Y6" t="n">
         <v>397.0026</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Z6" t="n">
         <v>399.9036</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AA6" t="n">
         <v>435.882</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AB6" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AC6" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -2845,58 +3922,85 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>38.491</v>
+      </c>
+      <c r="C7" t="n">
+        <v>39.0454</v>
+      </c>
+      <c r="D7" t="n">
+        <v>38.3425</v>
+      </c>
+      <c r="E7" t="n">
         <v>38.8028</v>
       </c>
-      <c r="C7" t="n">
+      <c r="F7" t="n">
         <v>35.863</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>33.8375</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>23 jul</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
+        <v>131</v>
+      </c>
+      <c r="M7" t="n">
+        <v>132.42</v>
+      </c>
+      <c r="N7" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="O7" t="n">
         <v>128.32</v>
       </c>
-      <c r="J7" t="n">
+      <c r="P7" t="n">
         <v>144.066</v>
       </c>
-      <c r="K7" t="n">
+      <c r="Q7" t="n">
         <v>173.9035</v>
       </c>
-      <c r="L7" t="n">
+      <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M7" t="n">
+      <c r="S7" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>22 jul</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="V7" t="n">
+        <v>398.8292</v>
+      </c>
+      <c r="W7" t="n">
+        <v>400.2465</v>
+      </c>
+      <c r="X7" t="n">
+        <v>386.2329</v>
+      </c>
+      <c r="Y7" t="n">
         <v>389.6066</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Z7" t="n">
         <v>399.4268</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AA7" t="n">
         <v>435.2723</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AB7" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AC7" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -2907,58 +4011,85 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>38.4019</v>
+      </c>
+      <c r="C8" t="n">
+        <v>38.6593</v>
+      </c>
+      <c r="D8" t="n">
+        <v>38.1594</v>
+      </c>
+      <c r="E8" t="n">
         <v>38.3871</v>
       </c>
-      <c r="C8" t="n">
+      <c r="F8" t="n">
         <v>35.9135</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>33.8757</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>24 jul</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
+        <v>130.88</v>
+      </c>
+      <c r="M8" t="n">
+        <v>141.32</v>
+      </c>
+      <c r="N8" t="n">
+        <v>130.86</v>
+      </c>
+      <c r="O8" t="n">
         <v>140.2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="P8" t="n">
         <v>143.9888</v>
       </c>
-      <c r="K8" t="n">
+      <c r="Q8" t="n">
         <v>173.4491</v>
       </c>
-      <c r="L8" t="n">
+      <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M8" t="n">
+      <c r="S8" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>23 jul</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="V8" t="n">
+        <v>389.2373</v>
+      </c>
+      <c r="W8" t="n">
+        <v>391.0439</v>
+      </c>
+      <c r="X8" t="n">
+        <v>376.6809</v>
+      </c>
+      <c r="Y8" t="n">
         <v>380.863</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Z8" t="n">
         <v>398.8242</v>
       </c>
-      <c r="R8" t="n">
+      <c r="AA8" t="n">
         <v>434.611</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AB8" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AC8" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -2969,58 +4100,85 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>37.5802</v>
+      </c>
+      <c r="C9" t="n">
+        <v>38.1099</v>
+      </c>
+      <c r="D9" t="n">
+        <v>37.4317</v>
+      </c>
+      <c r="E9" t="n">
         <v>37.9515</v>
       </c>
-      <c r="C9" t="n">
+      <c r="F9" t="n">
         <v>35.931</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>33.9167</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>27 jul</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
+        <v>142.38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>151.56</v>
+      </c>
+      <c r="N9" t="n">
+        <v>142</v>
+      </c>
+      <c r="O9" t="n">
         <v>151.28</v>
       </c>
-      <c r="J9" t="n">
+      <c r="P9" t="n">
         <v>144.0572</v>
       </c>
-      <c r="K9" t="n">
+      <c r="Q9" t="n">
         <v>173.0393</v>
       </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M9" t="n">
+      <c r="S9" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>24 jul</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="V9" t="n">
+        <v>386.3227</v>
+      </c>
+      <c r="W9" t="n">
+        <v>388.299</v>
+      </c>
+      <c r="X9" t="n">
+        <v>379.9348</v>
+      </c>
+      <c r="Y9" t="n">
         <v>380.9828</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v>398.3214</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AA9" t="n">
         <v>433.8946</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AB9" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AC9" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3031,58 +4189,85 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>37.7139</v>
+      </c>
+      <c r="C10" t="n">
+        <v>38.0109</v>
+      </c>
+      <c r="D10" t="n">
         <v>37.4713</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
+        <v>37.4713</v>
+      </c>
+      <c r="F10" t="n">
         <v>35.9372</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
         <v>33.9548</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>28 jul</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>159.76</v>
+      </c>
+      <c r="N10" t="n">
+        <v>151</v>
+      </c>
+      <c r="O10" t="n">
         <v>159.24</v>
       </c>
-      <c r="J10" t="n">
+      <c r="P10" t="n">
         <v>144.1076</v>
       </c>
-      <c r="K10" t="n">
+      <c r="Q10" t="n">
         <v>172.6663</v>
       </c>
-      <c r="L10" t="n">
+      <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M10" t="n">
+      <c r="S10" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>27 jul</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="V10" t="n">
+        <v>389.347</v>
+      </c>
+      <c r="W10" t="n">
+        <v>393.4593</v>
+      </c>
+      <c r="X10" t="n">
+        <v>387.261</v>
+      </c>
+      <c r="Y10" t="n">
         <v>388.3689</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v>398.0172</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AA10" t="n">
         <v>433.238</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AB10" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AC10" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3093,58 +4278,85 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>38.0653</v>
+      </c>
+      <c r="C11" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="D11" t="n">
+        <v>37.7089</v>
+      </c>
+      <c r="E11" t="n">
         <v>38.4415</v>
       </c>
-      <c r="C11" t="n">
+      <c r="F11" t="n">
         <v>35.9692</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="n">
         <v>33.9987</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>29 jul</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="M11" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>156.48</v>
+      </c>
+      <c r="O11" t="n">
         <v>162.04</v>
       </c>
-      <c r="J11" t="n">
+      <c r="P11" t="n">
         <v>144.28</v>
       </c>
-      <c r="K11" t="n">
+      <c r="Q11" t="n">
         <v>172.343</v>
       </c>
-      <c r="L11" t="n">
+      <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M11" t="n">
+      <c r="S11" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>28 jul</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="V11" t="n">
+        <v>392.4213</v>
+      </c>
+      <c r="W11" t="n">
+        <v>399.5678</v>
+      </c>
+      <c r="X11" t="n">
+        <v>390.5647</v>
+      </c>
+      <c r="Y11" t="n">
         <v>392.6109</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Z11" t="n">
         <v>397.7139</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AA11" t="n">
         <v>432.5982</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AB11" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AC11" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3155,58 +4367,85 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>38.6098</v>
+      </c>
+      <c r="C12" t="n">
+        <v>39.1444</v>
+      </c>
+      <c r="D12" t="n">
+        <v>38.3277</v>
+      </c>
+      <c r="E12" t="n">
         <v>38.5108</v>
       </c>
-      <c r="C12" t="n">
+      <c r="F12" t="n">
         <v>35.9978</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>34.0424</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>30 jul</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>163.16</v>
+      </c>
+      <c r="N12" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="O12" t="n">
         <v>155.92</v>
       </c>
-      <c r="J12" t="n">
+      <c r="P12" t="n">
         <v>144.3804</v>
       </c>
-      <c r="K12" t="n">
+      <c r="Q12" t="n">
         <v>171.9849</v>
       </c>
-      <c r="L12" t="n">
+      <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M12" t="n">
+      <c r="S12" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>29 jul</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="V12" t="n">
+        <v>392.6608</v>
+      </c>
+      <c r="W12" t="n">
+        <v>400.4961</v>
+      </c>
+      <c r="X12" t="n">
+        <v>388.0095</v>
+      </c>
+      <c r="Y12" t="n">
         <v>389.8062</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Z12" t="n">
         <v>397.1057</v>
       </c>
-      <c r="R12" t="n">
+      <c r="AA12" t="n">
         <v>431.9565</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AB12" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AC12" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3217,58 +4456,85 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>38.6098</v>
+      </c>
+      <c r="C13" t="n">
+        <v>39.575</v>
+      </c>
+      <c r="D13" t="n">
+        <v>38.4464</v>
+      </c>
+      <c r="E13" t="n">
         <v>39.3226</v>
       </c>
-      <c r="C13" t="n">
+      <c r="F13" t="n">
         <v>36.0495</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
         <v>34.0907</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>31 jul</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>158.26</v>
+      </c>
+      <c r="N13" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="O13" t="n">
         <v>157.68</v>
       </c>
-      <c r="J13" t="n">
+      <c r="P13" t="n">
         <v>144.4984</v>
       </c>
-      <c r="K13" t="n">
+      <c r="Q13" t="n">
         <v>171.6292</v>
       </c>
-      <c r="L13" t="n">
+      <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M13" t="n">
+      <c r="S13" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>30 jul</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="V13" t="n">
+        <v>437.0772</v>
+      </c>
+      <c r="W13" t="n">
+        <v>457.8281</v>
+      </c>
+      <c r="X13" t="n">
+        <v>431.6275</v>
+      </c>
+      <c r="Y13" t="n">
         <v>450.2524</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Z13" t="n">
         <v>397.6741</v>
       </c>
-      <c r="R13" t="n">
+      <c r="AA13" t="n">
         <v>431.6738</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AB13" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AC13" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3279,58 +4545,85 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>38.3128</v>
+      </c>
+      <c r="C14" t="n">
         <v>39.4067</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
+        <v>38.2138</v>
+      </c>
+      <c r="E14" t="n">
+        <v>39.4067</v>
+      </c>
+      <c r="F14" t="n">
         <v>36.1112</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
         <v>34.1393</v>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>3 aug</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
+        <v>160</v>
+      </c>
+      <c r="M14" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="O14" t="n">
         <v>164.64</v>
       </c>
-      <c r="J14" t="n">
+      <c r="P14" t="n">
         <v>144.7016</v>
       </c>
-      <c r="K14" t="n">
+      <c r="Q14" t="n">
         <v>171.301</v>
       </c>
-      <c r="L14" t="n">
+      <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M14" t="n">
+      <c r="S14" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>31 jul</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="V14" t="n">
+        <v>449.1545</v>
+      </c>
+      <c r="W14" t="n">
+        <v>465.9628</v>
+      </c>
+      <c r="X14" t="n">
+        <v>448.4857</v>
+      </c>
+      <c r="Y14" t="n">
         <v>463.8468</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Z14" t="n">
         <v>398.6364</v>
       </c>
-      <c r="R14" t="n">
+      <c r="AA14" t="n">
         <v>431.4438</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AB14" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AC14" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3341,58 +4634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>39.3028</v>
+      </c>
+      <c r="C15" t="n">
+        <v>39.6443</v>
+      </c>
+      <c r="D15" t="n">
+        <v>38.2039</v>
+      </c>
+      <c r="E15" t="n">
         <v>38.486</v>
       </c>
-      <c r="C15" t="n">
+      <c r="F15" t="n">
         <v>36.1495</v>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" t="n">
         <v>34.1818</v>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>4 aug</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
+        <v>162.86</v>
+      </c>
+      <c r="M15" t="n">
+        <v>168.56</v>
+      </c>
+      <c r="N15" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="O15" t="n">
         <v>167.38</v>
       </c>
-      <c r="J15" t="n">
+      <c r="P15" t="n">
         <v>145.02</v>
       </c>
-      <c r="K15" t="n">
+      <c r="Q15" t="n">
         <v>170.9913</v>
       </c>
-      <c r="L15" t="n">
+      <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M15" t="n">
+      <c r="S15" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>3 aug</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="V15" t="n">
+        <v>475.2354</v>
+      </c>
+      <c r="W15" t="n">
+        <v>490.7262</v>
+      </c>
+      <c r="X15" t="n">
+        <v>474.1075</v>
+      </c>
+      <c r="Y15" t="n">
         <v>486.7337</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Z15" t="n">
         <v>399.9838</v>
       </c>
-      <c r="R15" t="n">
+      <c r="AA15" t="n">
         <v>431.3306</v>
       </c>
-      <c r="S15" t="n">
+      <c r="AB15" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AC15" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3403,58 +4723,85 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>38.4811</v>
+      </c>
+      <c r="C16" t="n">
+        <v>38.7632</v>
+      </c>
+      <c r="D16" t="n">
+        <v>37.9366</v>
+      </c>
+      <c r="E16" t="n">
         <v>38.0307</v>
       </c>
-      <c r="C16" t="n">
+      <c r="F16" t="n">
         <v>36.1966</v>
       </c>
-      <c r="D16" t="n">
+      <c r="G16" t="n">
         <v>34.2215</v>
       </c>
-      <c r="E16" t="n">
+      <c r="H16" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F16" t="n">
+      <c r="I16" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>5 aug</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
+        <v>167.92</v>
+      </c>
+      <c r="M16" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="O16" t="n">
         <v>169.26</v>
       </c>
-      <c r="J16" t="n">
+      <c r="P16" t="n">
         <v>145.4052</v>
       </c>
-      <c r="K16" t="n">
+      <c r="Q16" t="n">
         <v>170.7022</v>
       </c>
-      <c r="L16" t="n">
+      <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M16" t="n">
+      <c r="S16" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>4 aug</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="V16" t="n">
+        <v>479.9964</v>
+      </c>
+      <c r="W16" t="n">
+        <v>498.5016</v>
+      </c>
+      <c r="X16" t="n">
+        <v>478.2697</v>
+      </c>
+      <c r="Y16" t="n">
         <v>491.884</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Z16" t="n">
         <v>401.4555</v>
       </c>
-      <c r="R16" t="n">
+      <c r="AA16" t="n">
         <v>431.2438</v>
       </c>
-      <c r="S16" t="n">
+      <c r="AB16" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T16" t="n">
+      <c r="AC16" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3465,58 +4812,85 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>38.0752</v>
+      </c>
+      <c r="C17" t="n">
+        <v>38.4069</v>
+      </c>
+      <c r="D17" t="n">
+        <v>37.9168</v>
+      </c>
+      <c r="E17" t="n">
         <v>38.392</v>
       </c>
-      <c r="C17" t="n">
+      <c r="F17" t="n">
         <v>36.2474</v>
       </c>
-      <c r="D17" t="n">
+      <c r="G17" t="n">
         <v>34.2607</v>
       </c>
-      <c r="E17" t="n">
+      <c r="H17" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F17" t="n">
+      <c r="I17" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>6 aug</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
+        <v>171.44</v>
+      </c>
+      <c r="M17" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>168.08</v>
+      </c>
+      <c r="O17" t="n">
         <v>170.98</v>
       </c>
-      <c r="J17" t="n">
+      <c r="P17" t="n">
         <v>145.7928</v>
       </c>
-      <c r="K17" t="n">
+      <c r="Q17" t="n">
         <v>170.384</v>
       </c>
-      <c r="L17" t="n">
+      <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M17" t="n">
+      <c r="S17" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>5 aug</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="V17" t="n">
+        <v>495.4273</v>
+      </c>
+      <c r="W17" t="n">
+        <v>497.3038</v>
+      </c>
+      <c r="X17" t="n">
+        <v>484.7674</v>
+      </c>
+      <c r="Y17" t="n">
         <v>486.5441</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Z17" t="n">
         <v>402.8307</v>
       </c>
-      <c r="R17" t="n">
+      <c r="AA17" t="n">
         <v>431.1393</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AB17" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T17" t="n">
+      <c r="AC17" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3527,58 +4901,85 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>38.5207</v>
+      </c>
+      <c r="C18" t="n">
+        <v>38.5999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>37.897</v>
+      </c>
+      <c r="E18" t="n">
         <v>38.0059</v>
       </c>
-      <c r="C18" t="n">
+      <c r="F18" t="n">
         <v>36.2952</v>
       </c>
-      <c r="D18" t="n">
+      <c r="G18" t="n">
         <v>34.294</v>
       </c>
-      <c r="E18" t="n">
+      <c r="H18" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F18" t="n">
+      <c r="I18" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>7 aug</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="L18" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="M18" t="n">
+        <v>179.56</v>
+      </c>
+      <c r="N18" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="O18" t="n">
         <v>177.96</v>
       </c>
-      <c r="J18" t="n">
+      <c r="P18" t="n">
         <v>146.2468</v>
       </c>
-      <c r="K18" t="n">
+      <c r="Q18" t="n">
         <v>170.0918</v>
       </c>
-      <c r="L18" t="n">
+      <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M18" t="n">
+      <c r="S18" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>6 aug</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="V18" t="n">
+        <v>487.632</v>
+      </c>
+      <c r="W18" t="n">
+        <v>500.6176</v>
+      </c>
+      <c r="X18" t="n">
+        <v>487.6021</v>
+      </c>
+      <c r="Y18" t="n">
         <v>498.9207</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Z18" t="n">
         <v>404.5041</v>
       </c>
-      <c r="R18" t="n">
+      <c r="AA18" t="n">
         <v>431.087</v>
       </c>
-      <c r="S18" t="n">
+      <c r="AB18" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T18" t="n">
+      <c r="AC18" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3589,58 +4990,85 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>38.0356</v>
+      </c>
+      <c r="C19" t="n">
+        <v>38.4366</v>
+      </c>
+      <c r="D19" t="n">
+        <v>37.803</v>
+      </c>
+      <c r="E19" t="n">
         <v>38.4019</v>
       </c>
-      <c r="C19" t="n">
+      <c r="F19" t="n">
         <v>36.3315</v>
       </c>
-      <c r="D19" t="n">
+      <c r="G19" t="n">
         <v>34.3294</v>
       </c>
-      <c r="E19" t="n">
+      <c r="H19" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>10 aug</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="L19" t="n">
+        <v>178.92</v>
+      </c>
+      <c r="M19" t="n">
+        <v>179.96</v>
+      </c>
+      <c r="N19" t="n">
+        <v>175.86</v>
+      </c>
+      <c r="O19" t="n">
         <v>179.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="P19" t="n">
         <v>146.4748</v>
       </c>
-      <c r="K19" t="n">
+      <c r="Q19" t="n">
         <v>169.8238</v>
       </c>
-      <c r="L19" t="n">
+      <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M19" t="n">
+      <c r="S19" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>7 aug</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="V19" t="n">
+        <v>498.272</v>
+      </c>
+      <c r="W19" t="n">
+        <v>504.2308</v>
+      </c>
+      <c r="X19" t="n">
+        <v>497.7929</v>
+      </c>
+      <c r="Y19" t="n">
         <v>499.0505</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Z19" t="n">
         <v>406.2472</v>
       </c>
-      <c r="R19" t="n">
+      <c r="AA19" t="n">
         <v>431.0194</v>
       </c>
-      <c r="S19" t="n">
+      <c r="AB19" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T19" t="n">
+      <c r="AC19" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3651,58 +5079,85 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>38.7385</v>
+      </c>
+      <c r="C20" t="n">
+        <v>39.0058</v>
+      </c>
+      <c r="D20" t="n">
+        <v>38.6148</v>
+      </c>
+      <c r="E20" t="n">
         <v>38.9662</v>
       </c>
-      <c r="C20" t="n">
+      <c r="F20" t="n">
         <v>36.374</v>
       </c>
-      <c r="D20" t="n">
+      <c r="G20" t="n">
         <v>34.3685</v>
       </c>
-      <c r="E20" t="n">
+      <c r="H20" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F20" t="n">
+      <c r="I20" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>11 aug</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="L20" t="n">
+        <v>180</v>
+      </c>
+      <c r="M20" t="n">
+        <v>183.24</v>
+      </c>
+      <c r="N20" t="n">
+        <v>178.14</v>
+      </c>
+      <c r="O20" t="n">
         <v>180.7</v>
       </c>
-      <c r="J20" t="n">
+      <c r="P20" t="n">
         <v>146.8316</v>
       </c>
-      <c r="K20" t="n">
+      <c r="Q20" t="n">
         <v>169.5375</v>
       </c>
-      <c r="L20" t="n">
+      <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M20" t="n">
+      <c r="S20" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>10 aug</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="V20" t="n">
+        <v>502.4941</v>
+      </c>
+      <c r="W20" t="n">
+        <v>512.7646999999999</v>
+      </c>
+      <c r="X20" t="n">
+        <v>501.3262</v>
+      </c>
+      <c r="Y20" t="n">
         <v>505.1091</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Z20" t="n">
         <v>407.8257</v>
       </c>
-      <c r="R20" t="n">
+      <c r="AA20" t="n">
         <v>430.9778</v>
       </c>
-      <c r="S20" t="n">
+      <c r="AB20" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T20" t="n">
+      <c r="AC20" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3713,58 +5168,85 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>38.8573</v>
+      </c>
+      <c r="C21" t="n">
+        <v>38.986</v>
+      </c>
+      <c r="D21" t="n">
+        <v>38.3871</v>
+      </c>
+      <c r="E21" t="n">
         <v>38.6494</v>
       </c>
-      <c r="C21" t="n">
+      <c r="F21" t="n">
         <v>36.3981</v>
       </c>
-      <c r="D21" t="n">
+      <c r="G21" t="n">
         <v>34.4068</v>
       </c>
-      <c r="E21" t="n">
+      <c r="H21" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>12 aug</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>180.98</v>
+      </c>
+      <c r="N21" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="O21" t="n">
         <v>175.96</v>
       </c>
-      <c r="J21" t="n">
+      <c r="P21" t="n">
         <v>147.232</v>
       </c>
-      <c r="K21" t="n">
+      <c r="Q21" t="n">
         <v>169.2701</v>
       </c>
-      <c r="L21" t="n">
+      <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M21" t="n">
+      <c r="S21" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>11 aug</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="V21" t="n">
+        <v>503.3824</v>
+      </c>
+      <c r="W21" t="n">
+        <v>504.3805</v>
+      </c>
+      <c r="X21" t="n">
+        <v>498.6113</v>
+      </c>
+      <c r="Y21" t="n">
         <v>502.8633</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Z21" t="n">
         <v>408.895</v>
       </c>
-      <c r="R21" t="n">
+      <c r="AA21" t="n">
         <v>430.9106</v>
       </c>
-      <c r="S21" t="n">
+      <c r="AB21" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T21" t="n">
+      <c r="AC21" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3775,58 +5257,85 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>39</v>
+      </c>
+      <c r="C22" t="n">
+        <v>39.005</v>
+      </c>
+      <c r="D22" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E22" t="n">
         <v>38.605</v>
       </c>
-      <c r="C22" t="n">
+      <c r="F22" t="n">
         <v>36.4313</v>
       </c>
-      <c r="D22" t="n">
+      <c r="G22" t="n">
         <v>34.4429</v>
       </c>
-      <c r="E22" t="n">
+      <c r="H22" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F22" t="n">
+      <c r="I22" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>13 aug</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="L22" t="n">
+        <v>177.48</v>
+      </c>
+      <c r="M22" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="O22" t="n">
         <v>175.38</v>
       </c>
-      <c r="J22" t="n">
+      <c r="P22" t="n">
         <v>147.4496</v>
       </c>
-      <c r="K22" t="n">
+      <c r="Q22" t="n">
         <v>168.9889</v>
       </c>
-      <c r="L22" t="n">
+      <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M22" t="n">
+      <c r="S22" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>12 aug</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="V22" t="n">
+        <v>499.0505</v>
+      </c>
+      <c r="W22" t="n">
+        <v>500.5577</v>
+      </c>
+      <c r="X22" t="n">
+        <v>490.5964</v>
+      </c>
+      <c r="Y22" t="n">
         <v>491.5047</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Z22" t="n">
         <v>409.532</v>
       </c>
-      <c r="R22" t="n">
+      <c r="AA22" t="n">
         <v>430.7866</v>
       </c>
-      <c r="S22" t="n">
+      <c r="AB22" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T22" t="n">
+      <c r="AC22" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3837,58 +5346,85 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="C23" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="E23" t="n">
         <v>38.97</v>
       </c>
-      <c r="C23" t="n">
+      <c r="F23" t="n">
         <v>36.4703</v>
       </c>
-      <c r="D23" t="n">
+      <c r="G23" t="n">
         <v>34.4805</v>
       </c>
-      <c r="E23" t="n">
+      <c r="H23" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F23" t="n">
+      <c r="I23" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>14 aug</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="L23" t="n">
+        <v>182</v>
+      </c>
+      <c r="M23" t="n">
+        <v>185.74</v>
+      </c>
+      <c r="N23" t="n">
+        <v>179.28</v>
+      </c>
+      <c r="O23" t="n">
         <v>180.14</v>
       </c>
-      <c r="J23" t="n">
+      <c r="P23" t="n">
         <v>147.8228</v>
       </c>
-      <c r="K23" t="n">
+      <c r="Q23" t="n">
         <v>168.7386</v>
       </c>
-      <c r="L23" t="n">
+      <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M23" t="n">
+      <c r="S23" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>13 aug</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="V23" t="n">
+        <v>492.3431</v>
+      </c>
+      <c r="W23" t="n">
+        <v>500.398</v>
+      </c>
+      <c r="X23" t="n">
+        <v>492.0837</v>
+      </c>
+      <c r="Y23" t="n">
         <v>495.9464</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Z23" t="n">
         <v>410.6414</v>
       </c>
-      <c r="R23" t="n">
+      <c r="AA23" t="n">
         <v>430.6696</v>
       </c>
-      <c r="S23" t="n">
+      <c r="AB23" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T23" t="n">
+      <c r="AC23" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3899,58 +5435,85 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="C24" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="D24" t="n">
+        <v>38.765</v>
+      </c>
+      <c r="E24" t="n">
         <v>39.15</v>
       </c>
-      <c r="C24" t="n">
+      <c r="F24" t="n">
         <v>36.5118</v>
       </c>
-      <c r="D24" t="n">
+      <c r="G24" t="n">
         <v>34.5207</v>
       </c>
-      <c r="E24" t="n">
+      <c r="H24" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F24" t="n">
+      <c r="I24" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>17 aug</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="L24" t="n">
+        <v>178.94</v>
+      </c>
+      <c r="M24" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>177.66</v>
+      </c>
+      <c r="O24" t="n">
         <v>179.58</v>
       </c>
-      <c r="J24" t="n">
+      <c r="P24" t="n">
         <v>148.2524</v>
       </c>
-      <c r="K24" t="n">
+      <c r="Q24" t="n">
         <v>168.5337</v>
       </c>
-      <c r="L24" t="n">
+      <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M24" t="n">
+      <c r="S24" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>14 aug</t>
         </is>
       </c>
-      <c r="P24" t="n">
+      <c r="V24" t="n">
+        <v>495.4273</v>
+      </c>
+      <c r="W24" t="n">
+        <v>499.0705</v>
+      </c>
+      <c r="X24" t="n">
+        <v>492.9919</v>
+      </c>
+      <c r="Y24" t="n">
         <v>494.4691</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Z24" t="n">
         <v>412</v>
       </c>
-      <c r="R24" t="n">
+      <c r="AA24" t="n">
         <v>430.5061</v>
       </c>
-      <c r="S24" t="n">
+      <c r="AB24" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T24" t="n">
+      <c r="AC24" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -3961,58 +5524,85 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="C25" t="n">
+        <v>39.945</v>
+      </c>
+      <c r="D25" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="E25" t="n">
         <v>39.785</v>
       </c>
-      <c r="C25" t="n">
+      <c r="F25" t="n">
         <v>36.5781</v>
       </c>
-      <c r="D25" t="n">
+      <c r="G25" t="n">
         <v>34.5641</v>
       </c>
-      <c r="E25" t="n">
+      <c r="H25" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F25" t="n">
+      <c r="I25" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>18 aug</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="L25" t="n">
+        <v>179.14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>177.98</v>
+      </c>
+      <c r="O25" t="n">
         <v>182.5</v>
       </c>
-      <c r="J25" t="n">
+      <c r="P25" t="n">
         <v>148.8084</v>
       </c>
-      <c r="K25" t="n">
+      <c r="Q25" t="n">
         <v>168.3358</v>
       </c>
-      <c r="L25" t="n">
+      <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M25" t="n">
+      <c r="S25" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>17 aug</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="V25" t="n">
+        <v>489.2191</v>
+      </c>
+      <c r="W25" t="n">
+        <v>491.7343</v>
+      </c>
+      <c r="X25" t="n">
+        <v>477.5111</v>
+      </c>
+      <c r="Y25" t="n">
         <v>479.4474</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Z25" t="n">
         <v>413.044</v>
       </c>
-      <c r="R25" t="n">
+      <c r="AA25" t="n">
         <v>430.2151</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AB25" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T25" t="n">
+      <c r="AC25" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4023,58 +5613,85 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>39.835</v>
+      </c>
+      <c r="C26" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="D26" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="E26" t="n">
         <v>39.94</v>
       </c>
-      <c r="C26" t="n">
+      <c r="F26" t="n">
         <v>36.6336</v>
       </c>
-      <c r="D26" t="n">
+      <c r="G26" t="n">
         <v>34.6092</v>
       </c>
-      <c r="E26" t="n">
+      <c r="H26" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F26" t="n">
+      <c r="I26" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>19 aug</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="L26" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="M26" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="N26" t="n">
+        <v>180.38</v>
+      </c>
+      <c r="O26" t="n">
         <v>185.9</v>
       </c>
-      <c r="J26" t="n">
+      <c r="P26" t="n">
         <v>149.5324</v>
       </c>
-      <c r="K26" t="n">
+      <c r="Q26" t="n">
         <v>168.1618</v>
       </c>
-      <c r="L26" t="n">
+      <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M26" t="n">
+      <c r="S26" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>18 aug</t>
         </is>
       </c>
-      <c r="P26" t="n">
+      <c r="V26" t="n">
+        <v>480.6352</v>
+      </c>
+      <c r="W26" t="n">
+        <v>483.3601</v>
+      </c>
+      <c r="X26" t="n">
+        <v>476.2534</v>
+      </c>
+      <c r="Y26" t="n">
         <v>480.725</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Z26" t="n">
         <v>414.3408</v>
       </c>
-      <c r="R26" t="n">
+      <c r="AA26" t="n">
         <v>429.933</v>
       </c>
-      <c r="S26" t="n">
+      <c r="AB26" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T26" t="n">
+      <c r="AC26" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4085,58 +5702,85 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>39.865</v>
+      </c>
+      <c r="C27" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="D27" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E27" t="n">
         <v>40.28</v>
       </c>
-      <c r="C27" t="n">
+      <c r="F27" t="n">
         <v>36.6884</v>
       </c>
-      <c r="D27" t="n">
+      <c r="G27" t="n">
         <v>34.6545</v>
       </c>
-      <c r="E27" t="n">
+      <c r="H27" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F27" t="n">
+      <c r="I27" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>20 aug</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="L27" t="n">
+        <v>183.78</v>
+      </c>
+      <c r="M27" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>182.52</v>
+      </c>
+      <c r="O27" t="n">
         <v>185.64</v>
       </c>
-      <c r="J27" t="n">
+      <c r="P27" t="n">
         <v>150.4472</v>
       </c>
-      <c r="K27" t="n">
+      <c r="Q27" t="n">
         <v>167.9648</v>
       </c>
-      <c r="L27" t="n">
+      <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M27" t="n">
+      <c r="S27" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>19 aug</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="V27" t="n">
+        <v>479.168</v>
+      </c>
+      <c r="W27" t="n">
+        <v>488.3806</v>
+      </c>
+      <c r="X27" t="n">
+        <v>478.4593</v>
+      </c>
+      <c r="Y27" t="n">
         <v>483.4</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Z27" t="n">
         <v>415.7895</v>
       </c>
-      <c r="R27" t="n">
+      <c r="AA27" t="n">
         <v>429.7427</v>
       </c>
-      <c r="S27" t="n">
+      <c r="AB27" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T27" t="n">
+      <c r="AC27" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4147,58 +5791,85 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="D28" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="E28" t="n">
         <v>39.91</v>
       </c>
-      <c r="C28" t="n">
+      <c r="F28" t="n">
         <v>36.7478</v>
       </c>
-      <c r="D28" t="n">
+      <c r="G28" t="n">
         <v>34.6988</v>
       </c>
-      <c r="E28" t="n">
+      <c r="H28" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F28" t="n">
+      <c r="I28" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>21 aug</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="L28" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="M28" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="O28" t="n">
         <v>188.12</v>
       </c>
-      <c r="J28" t="n">
+      <c r="P28" t="n">
         <v>151.4044</v>
       </c>
-      <c r="K28" t="n">
+      <c r="Q28" t="n">
         <v>167.794</v>
       </c>
-      <c r="L28" t="n">
+      <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M28" t="n">
+      <c r="S28" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>20 aug</t>
         </is>
       </c>
-      <c r="P28" t="n">
+      <c r="V28" t="n">
+        <v>483.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>484.16</v>
+      </c>
+      <c r="X28" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="Y28" t="n">
         <v>481.15</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Z28" t="n">
         <v>417.3594</v>
       </c>
-      <c r="R28" t="n">
+      <c r="AA28" t="n">
         <v>429.5805</v>
       </c>
-      <c r="S28" t="n">
+      <c r="AB28" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T28" t="n">
+      <c r="AC28" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4209,58 +5880,85 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="C29" t="n">
+        <v>40.085</v>
+      </c>
+      <c r="D29" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="E29" t="n">
         <v>39.775</v>
       </c>
-      <c r="C29" t="n">
+      <c r="F29" t="n">
         <v>36.8369</v>
       </c>
-      <c r="D29" t="n">
+      <c r="G29" t="n">
         <v>34.7421</v>
       </c>
-      <c r="E29" t="n">
+      <c r="H29" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F29" t="n">
+      <c r="I29" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>24 aug</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="L29" t="n">
+        <v>186.86</v>
+      </c>
+      <c r="M29" t="n">
+        <v>188.16</v>
+      </c>
+      <c r="N29" t="n">
+        <v>185.52</v>
+      </c>
+      <c r="O29" t="n">
         <v>187.2</v>
       </c>
-      <c r="J29" t="n">
+      <c r="P29" t="n">
         <v>152.2848</v>
       </c>
-      <c r="K29" t="n">
+      <c r="Q29" t="n">
         <v>167.6093</v>
       </c>
-      <c r="L29" t="n">
+      <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M29" t="n">
+      <c r="S29" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>21 aug</t>
         </is>
       </c>
-      <c r="P29" t="n">
+      <c r="V29" t="n">
+        <v>479.88</v>
+      </c>
+      <c r="W29" t="n">
+        <v>486.36</v>
+      </c>
+      <c r="X29" t="n">
+        <v>478.53</v>
+      </c>
+      <c r="Y29" t="n">
         <v>483.24</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Z29" t="n">
         <v>419.092</v>
       </c>
-      <c r="R29" t="n">
+      <c r="AA29" t="n">
         <v>429.4327</v>
       </c>
-      <c r="S29" t="n">
+      <c r="AB29" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T29" t="n">
+      <c r="AC29" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4271,58 +5969,85 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="C30" t="n">
+        <v>39.915</v>
+      </c>
+      <c r="D30" t="n">
+        <v>39.385</v>
+      </c>
+      <c r="E30" t="n">
         <v>39.6</v>
       </c>
-      <c r="C30" t="n">
+      <c r="F30" t="n">
         <v>36.926</v>
       </c>
-      <c r="D30" t="n">
+      <c r="G30" t="n">
         <v>34.783</v>
       </c>
-      <c r="E30" t="n">
+      <c r="H30" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F30" t="n">
+      <c r="I30" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>25 aug</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="L30" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>187.62</v>
+      </c>
+      <c r="N30" t="n">
+        <v>182.74</v>
+      </c>
+      <c r="O30" t="n">
         <v>185.46</v>
       </c>
-      <c r="J30" t="n">
+      <c r="P30" t="n">
         <v>153.136</v>
       </c>
-      <c r="K30" t="n">
+      <c r="Q30" t="n">
         <v>167.4651</v>
       </c>
-      <c r="L30" t="n">
+      <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M30" t="n">
+      <c r="S30" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>24 aug</t>
         </is>
       </c>
-      <c r="P30" t="n">
+      <c r="V30" t="n">
+        <v>483.21</v>
+      </c>
+      <c r="W30" t="n">
+        <v>490.61</v>
+      </c>
+      <c r="X30" t="n">
+        <v>481.86</v>
+      </c>
+      <c r="Y30" t="n">
         <v>487.31</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Z30" t="n">
         <v>421.046</v>
       </c>
-      <c r="R30" t="n">
+      <c r="AA30" t="n">
         <v>429.3185</v>
       </c>
-      <c r="S30" t="n">
+      <c r="AB30" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T30" t="n">
+      <c r="AC30" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4333,58 +6058,85 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>39.275</v>
+      </c>
+      <c r="C31" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="D31" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="E31" t="n">
         <v>39.42</v>
       </c>
-      <c r="C31" t="n">
+      <c r="F31" t="n">
         <v>37.0192</v>
       </c>
-      <c r="D31" t="n">
+      <c r="G31" t="n">
         <v>34.8202</v>
       </c>
-      <c r="E31" t="n">
+      <c r="H31" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F31" t="n">
+      <c r="I31" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>26 aug</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="L31" t="n">
+        <v>179.92</v>
+      </c>
+      <c r="M31" t="n">
+        <v>182.16</v>
+      </c>
+      <c r="N31" t="n">
+        <v>176.82</v>
+      </c>
+      <c r="O31" t="n">
         <v>180.02</v>
       </c>
-      <c r="J31" t="n">
+      <c r="P31" t="n">
         <v>153.9128</v>
       </c>
-      <c r="K31" t="n">
+      <c r="Q31" t="n">
         <v>167.3049</v>
       </c>
-      <c r="L31" t="n">
+      <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M31" t="n">
+      <c r="S31" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>25 aug</t>
         </is>
       </c>
-      <c r="P31" t="n">
+      <c r="V31" t="n">
+        <v>485.44</v>
+      </c>
+      <c r="W31" t="n">
+        <v>492.44</v>
+      </c>
+      <c r="X31" t="n">
+        <v>484.3</v>
+      </c>
+      <c r="Y31" t="n">
         <v>491.71</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Z31" t="n">
         <v>423.0801</v>
       </c>
-      <c r="R31" t="n">
+      <c r="AA31" t="n">
         <v>429.262</v>
       </c>
-      <c r="S31" t="n">
+      <c r="AB31" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T31" t="n">
+      <c r="AC31" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4395,58 +6147,85 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>39.295</v>
+      </c>
+      <c r="D32" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="E32" t="n">
         <v>38.76</v>
       </c>
-      <c r="C32" t="n">
+      <c r="F32" t="n">
         <v>37.117</v>
       </c>
-      <c r="D32" t="n">
+      <c r="G32" t="n">
         <v>34.8559</v>
       </c>
-      <c r="E32" t="n">
+      <c r="H32" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F32" t="n">
+      <c r="I32" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>27 aug</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="L32" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>181.14</v>
+      </c>
+      <c r="O32" t="n">
         <v>189.88</v>
       </c>
-      <c r="J32" t="n">
+      <c r="P32" t="n">
         <v>155.0132</v>
       </c>
-      <c r="K32" t="n">
+      <c r="Q32" t="n">
         <v>167.1911</v>
       </c>
-      <c r="L32" t="n">
+      <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M32" t="n">
+      <c r="S32" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>26 aug</t>
         </is>
       </c>
-      <c r="P32" t="n">
+      <c r="V32" t="n">
+        <v>487.85</v>
+      </c>
+      <c r="W32" t="n">
+        <v>497.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>487.31</v>
+      </c>
+      <c r="Y32" t="n">
         <v>496.37</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Z32" t="n">
         <v>425.0273</v>
       </c>
-      <c r="R32" t="n">
+      <c r="AA32" t="n">
         <v>429.2786</v>
       </c>
-      <c r="S32" t="n">
+      <c r="AB32" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T32" t="n">
+      <c r="AC32" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4457,58 +6236,85 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>39</v>
+      </c>
+      <c r="C33" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="D33" t="n">
+        <v>38.845</v>
+      </c>
+      <c r="E33" t="n">
         <v>39.145</v>
       </c>
-      <c r="C33" t="n">
+      <c r="F33" t="n">
         <v>37.2162</v>
       </c>
-      <c r="D33" t="n">
+      <c r="G33" t="n">
         <v>34.8941</v>
       </c>
-      <c r="E33" t="n">
+      <c r="H33" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F33" t="n">
+      <c r="I33" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>28 aug</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="L33" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>191.94</v>
+      </c>
+      <c r="N33" t="n">
+        <v>187.98</v>
+      </c>
+      <c r="O33" t="n">
         <v>191.32</v>
       </c>
-      <c r="J33" t="n">
+      <c r="P33" t="n">
         <v>156.1568</v>
       </c>
-      <c r="K33" t="n">
+      <c r="Q33" t="n">
         <v>167.0806</v>
       </c>
-      <c r="L33" t="n">
+      <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M33" t="n">
+      <c r="S33" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>27 aug</t>
         </is>
       </c>
-      <c r="P33" t="n">
+      <c r="V33" t="n">
+        <v>494.88</v>
+      </c>
+      <c r="W33" t="n">
+        <v>506.48</v>
+      </c>
+      <c r="X33" t="n">
+        <v>490.08</v>
+      </c>
+      <c r="Y33" t="n">
         <v>505.06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Z33" t="n">
         <v>427.2667</v>
       </c>
-      <c r="R33" t="n">
+      <c r="AA33" t="n">
         <v>429.3401</v>
       </c>
-      <c r="S33" t="n">
+      <c r="AB33" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T33" t="n">
+      <c r="AC33" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4519,58 +6325,85 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="C34" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="D34" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="E34" t="n">
         <v>39.335</v>
       </c>
-      <c r="C34" t="n">
+      <c r="F34" t="n">
         <v>37.3111</v>
       </c>
-      <c r="D34" t="n">
+      <c r="G34" t="n">
         <v>34.9333</v>
       </c>
-      <c r="E34" t="n">
+      <c r="H34" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F34" t="n">
+      <c r="I34" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>31 aug</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="L34" t="n">
+        <v>188.46</v>
+      </c>
+      <c r="M34" t="n">
+        <v>192.12</v>
+      </c>
+      <c r="N34" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="O34" t="n">
         <v>190.9</v>
       </c>
-      <c r="J34" t="n">
+      <c r="P34" t="n">
         <v>157.3304</v>
       </c>
-      <c r="K34" t="n">
+      <c r="Q34" t="n">
         <v>166.9613</v>
       </c>
-      <c r="L34" t="n">
+      <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M34" t="n">
+      <c r="S34" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>28 aug</t>
         </is>
       </c>
-      <c r="P34" t="n">
+      <c r="V34" t="n">
+        <v>505.33</v>
+      </c>
+      <c r="W34" t="n">
+        <v>517.78</v>
+      </c>
+      <c r="X34" t="n">
+        <v>504.87</v>
+      </c>
+      <c r="Y34" t="n">
         <v>513.53</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Z34" t="n">
         <v>429.9734</v>
       </c>
-      <c r="R34" t="n">
+      <c r="AA34" t="n">
         <v>429.3984</v>
       </c>
-      <c r="S34" t="n">
+      <c r="AB34" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T34" t="n">
+      <c r="AC34" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4581,58 +6414,85 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="C35" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="D35" t="n">
+        <v>39.645</v>
+      </c>
+      <c r="E35" t="n">
         <v>40.155</v>
       </c>
-      <c r="C35" t="n">
+      <c r="F35" t="n">
         <v>37.4239</v>
       </c>
-      <c r="D35" t="n">
+      <c r="G35" t="n">
         <v>34.9763</v>
       </c>
-      <c r="E35" t="n">
+      <c r="H35" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F35" t="n">
+      <c r="I35" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>1 sep</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="L35" t="n">
+        <v>186</v>
+      </c>
+      <c r="M35" t="n">
+        <v>187.86</v>
+      </c>
+      <c r="N35" t="n">
+        <v>183.32</v>
+      </c>
+      <c r="O35" t="n">
         <v>184.26</v>
       </c>
-      <c r="J35" t="n">
+      <c r="P35" t="n">
         <v>158.3252</v>
       </c>
-      <c r="K35" t="n">
+      <c r="Q35" t="n">
         <v>166.8103</v>
       </c>
-      <c r="L35" t="n">
+      <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M35" t="n">
+      <c r="S35" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>31 aug</t>
         </is>
       </c>
-      <c r="P35" t="n">
+      <c r="V35" t="n">
+        <v>510.38</v>
+      </c>
+      <c r="W35" t="n">
+        <v>512.1900000000001</v>
+      </c>
+      <c r="X35" t="n">
+        <v>506.39</v>
+      </c>
+      <c r="Y35" t="n">
         <v>507.29</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Z35" t="n">
         <v>432.5454</v>
       </c>
-      <c r="R35" t="n">
+      <c r="AA35" t="n">
         <v>429.4122</v>
       </c>
-      <c r="S35" t="n">
+      <c r="AB35" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T35" t="n">
+      <c r="AC35" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4643,58 +6503,85 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="C36" t="n">
+        <v>40.615</v>
+      </c>
+      <c r="D36" t="n">
+        <v>39.975</v>
+      </c>
+      <c r="E36" t="n">
         <v>40.21</v>
       </c>
-      <c r="C36" t="n">
+      <c r="F36" t="n">
         <v>37.5499</v>
       </c>
-      <c r="D36" t="n">
+      <c r="G36" t="n">
         <v>35.0217</v>
       </c>
-      <c r="E36" t="n">
+      <c r="H36" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F36" t="n">
+      <c r="I36" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>2 sep</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="L36" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="M36" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>180.72</v>
+      </c>
+      <c r="O36" t="n">
         <v>181.44</v>
       </c>
-      <c r="J36" t="n">
+      <c r="P36" t="n">
         <v>159.2568</v>
       </c>
-      <c r="K36" t="n">
+      <c r="Q36" t="n">
         <v>166.6796</v>
       </c>
-      <c r="L36" t="n">
+      <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M36" t="n">
+      <c r="S36" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>1 sep</t>
         </is>
       </c>
-      <c r="P36" t="n">
+      <c r="V36" t="n">
+        <v>497.52</v>
+      </c>
+      <c r="W36" t="n">
+        <v>505.97</v>
+      </c>
+      <c r="X36" t="n">
+        <v>496.78</v>
+      </c>
+      <c r="Y36" t="n">
         <v>501.02</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Z36" t="n">
         <v>435.2328</v>
       </c>
-      <c r="R36" t="n">
+      <c r="AA36" t="n">
         <v>429.3825</v>
       </c>
-      <c r="S36" t="n">
+      <c r="AB36" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T36" t="n">
+      <c r="AC36" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4705,58 +6592,85 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>40.095</v>
+      </c>
+      <c r="C37" t="n">
+        <v>40.215</v>
+      </c>
+      <c r="D37" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="E37" t="n">
         <v>40.04</v>
       </c>
-      <c r="C37" t="n">
+      <c r="F37" t="n">
         <v>37.6767</v>
       </c>
-      <c r="D37" t="n">
+      <c r="G37" t="n">
         <v>35.0679</v>
       </c>
-      <c r="E37" t="n">
+      <c r="H37" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F37" t="n">
+      <c r="I37" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>3 sep</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="L37" t="n">
+        <v>182.08</v>
+      </c>
+      <c r="M37" t="n">
+        <v>187.56</v>
+      </c>
+      <c r="N37" t="n">
+        <v>182</v>
+      </c>
+      <c r="O37" t="n">
         <v>185.58</v>
       </c>
-      <c r="J37" t="n">
+      <c r="P37" t="n">
         <v>160.3228</v>
       </c>
-      <c r="K37" t="n">
+      <c r="Q37" t="n">
         <v>166.5898</v>
       </c>
-      <c r="L37" t="n">
+      <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M37" t="n">
+      <c r="S37" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>2 sep</t>
         </is>
       </c>
-      <c r="P37" t="n">
+      <c r="V37" t="n">
+        <v>499.85</v>
+      </c>
+      <c r="W37" t="n">
+        <v>500.27</v>
+      </c>
+      <c r="X37" t="n">
+        <v>493.81</v>
+      </c>
+      <c r="Y37" t="n">
         <v>496.82</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Z37" t="n">
         <v>437.7045</v>
       </c>
-      <c r="R37" t="n">
+      <c r="AA37" t="n">
         <v>429.3706</v>
       </c>
-      <c r="S37" t="n">
+      <c r="AB37" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T37" t="n">
+      <c r="AC37" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4767,58 +6681,85 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>40.145</v>
+      </c>
+      <c r="C38" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="D38" t="n">
+        <v>39.665</v>
+      </c>
+      <c r="E38" t="n">
         <v>40.105</v>
       </c>
-      <c r="C38" t="n">
+      <c r="F38" t="n">
         <v>37.8115</v>
       </c>
-      <c r="D38" t="n">
+      <c r="G38" t="n">
         <v>35.113</v>
       </c>
-      <c r="E38" t="n">
+      <c r="H38" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F38" t="n">
+      <c r="I38" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>4 sep</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="L38" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="N38" t="n">
+        <v>184.96</v>
+      </c>
+      <c r="O38" t="n">
         <v>185.68</v>
       </c>
-      <c r="J38" t="n">
+      <c r="P38" t="n">
         <v>161.3336</v>
       </c>
-      <c r="K38" t="n">
+      <c r="Q38" t="n">
         <v>166.5086</v>
       </c>
-      <c r="L38" t="n">
+      <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M38" t="n">
+      <c r="S38" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>3 sep</t>
         </is>
       </c>
-      <c r="P38" t="n">
+      <c r="V38" t="n">
+        <v>501.66</v>
+      </c>
+      <c r="W38" t="n">
+        <v>515.65</v>
+      </c>
+      <c r="X38" t="n">
+        <v>500.8</v>
+      </c>
+      <c r="Y38" t="n">
         <v>510.12</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Z38" t="n">
         <v>440.6114</v>
       </c>
-      <c r="R38" t="n">
+      <c r="AA38" t="n">
         <v>429.3912</v>
       </c>
-      <c r="S38" t="n">
+      <c r="AB38" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T38" t="n">
+      <c r="AC38" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4829,58 +6770,85 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="C39" t="n">
+        <v>40.845</v>
+      </c>
+      <c r="D39" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="E39" t="n">
         <v>40.56</v>
       </c>
-      <c r="C39" t="n">
+      <c r="F39" t="n">
         <v>37.9551</v>
       </c>
-      <c r="D39" t="n">
+      <c r="G39" t="n">
         <v>35.1619</v>
       </c>
-      <c r="E39" t="n">
+      <c r="H39" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F39" t="n">
+      <c r="I39" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>7 sep</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="L39" t="n">
+        <v>183.56</v>
+      </c>
+      <c r="M39" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>179.92</v>
+      </c>
+      <c r="O39" t="n">
         <v>182.8</v>
       </c>
-      <c r="J39" t="n">
+      <c r="P39" t="n">
         <v>162.2568</v>
       </c>
-      <c r="K39" t="n">
+      <c r="Q39" t="n">
         <v>166.4122</v>
       </c>
-      <c r="L39" t="n">
+      <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M39" t="n">
+      <c r="S39" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>4 sep</t>
         </is>
       </c>
-      <c r="P39" t="n">
+      <c r="V39" t="n">
+        <v>510</v>
+      </c>
+      <c r="W39" t="n">
+        <v>511</v>
+      </c>
+      <c r="X39" t="n">
+        <v>499.36</v>
+      </c>
+      <c r="Y39" t="n">
         <v>499.7</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Z39" t="n">
         <v>443.5621</v>
       </c>
-      <c r="R39" t="n">
+      <c r="AA39" t="n">
         <v>429.3729</v>
       </c>
-      <c r="S39" t="n">
+      <c r="AB39" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T39" t="n">
+      <c r="AC39" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4891,58 +6859,85 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="C40" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="D40" t="n">
+        <v>40.6325</v>
+      </c>
+      <c r="E40" t="n">
         <v>40.855</v>
       </c>
-      <c r="C40" t="n">
+      <c r="F40" t="n">
         <v>38.0977</v>
       </c>
-      <c r="D40" t="n">
+      <c r="G40" t="n">
         <v>35.2131</v>
       </c>
-      <c r="E40" t="n">
+      <c r="H40" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F40" t="n">
+      <c r="I40" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>8 sep</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="L40" t="n">
+        <v>182.32</v>
+      </c>
+      <c r="M40" t="n">
+        <v>183.76</v>
+      </c>
+      <c r="N40" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="O40" t="n">
         <v>181.7</v>
       </c>
-      <c r="J40" t="n">
+      <c r="P40" t="n">
         <v>163.2108</v>
       </c>
-      <c r="K40" t="n">
+      <c r="Q40" t="n">
         <v>166.3049</v>
       </c>
-      <c r="L40" t="n">
+      <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M40" t="n">
+      <c r="S40" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>8 sep</t>
         </is>
       </c>
-      <c r="P40" t="n">
+      <c r="V40" t="n">
+        <v>493.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>495.19</v>
+      </c>
+      <c r="X40" t="n">
+        <v>490.15</v>
+      </c>
+      <c r="Y40" t="n">
         <v>493.95</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Z40" t="n">
         <v>445.9957</v>
       </c>
-      <c r="R40" t="n">
+      <c r="AA40" t="n">
         <v>429.3939</v>
       </c>
-      <c r="S40" t="n">
+      <c r="AB40" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T40" t="n">
+      <c r="AC40" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -4953,58 +6948,85 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>41.385</v>
+      </c>
+      <c r="D41" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="E41" t="n">
         <v>40.94</v>
       </c>
-      <c r="C41" t="n">
+      <c r="F41" t="n">
         <v>38.2513</v>
       </c>
-      <c r="D41" t="n">
+      <c r="G41" t="n">
         <v>35.2646</v>
       </c>
-      <c r="E41" t="n">
+      <c r="H41" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F41" t="n">
+      <c r="I41" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>9 sep</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="L41" t="n">
+        <v>183</v>
+      </c>
+      <c r="M41" t="n">
+        <v>187.04</v>
+      </c>
+      <c r="N41" t="n">
+        <v>181.36</v>
+      </c>
+      <c r="O41" t="n">
         <v>182.86</v>
       </c>
-      <c r="J41" t="n">
+      <c r="P41" t="n">
         <v>164.0504</v>
       </c>
-      <c r="K41" t="n">
+      <c r="Q41" t="n">
         <v>166.2113</v>
       </c>
-      <c r="L41" t="n">
+      <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M41" t="n">
+      <c r="S41" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>9 sep</t>
         </is>
       </c>
-      <c r="P41" t="n">
+      <c r="V41" t="n">
+        <v>493.07</v>
+      </c>
+      <c r="W41" t="n">
+        <v>494.39</v>
+      </c>
+      <c r="X41" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="Y41" t="n">
         <v>491.65</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Z41" t="n">
         <v>448.4712</v>
       </c>
-      <c r="R41" t="n">
+      <c r="AA41" t="n">
         <v>429.4364</v>
       </c>
-      <c r="S41" t="n">
+      <c r="AB41" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T41" t="n">
+      <c r="AC41" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5015,58 +7037,85 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="C42" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="D42" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="E42" t="n">
         <v>41.23</v>
       </c>
-      <c r="C42" t="n">
+      <c r="F42" t="n">
         <v>38.4034</v>
       </c>
-      <c r="D42" t="n">
+      <c r="G42" t="n">
         <v>35.3174</v>
       </c>
-      <c r="E42" t="n">
+      <c r="H42" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F42" t="n">
+      <c r="I42" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>10 sep</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="L42" t="n">
+        <v>180</v>
+      </c>
+      <c r="M42" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="O42" t="n">
         <v>177.82</v>
       </c>
-      <c r="J42" t="n">
+      <c r="P42" t="n">
         <v>164.7724</v>
       </c>
-      <c r="K42" t="n">
+      <c r="Q42" t="n">
         <v>166.0803</v>
       </c>
-      <c r="L42" t="n">
+      <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M42" t="n">
+      <c r="S42" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>10 sep</t>
         </is>
       </c>
-      <c r="P42" t="n">
+      <c r="V42" t="n">
+        <v>488.32</v>
+      </c>
+      <c r="W42" t="n">
+        <v>494.52</v>
+      </c>
+      <c r="X42" t="n">
+        <v>486</v>
+      </c>
+      <c r="Y42" t="n">
         <v>492.44</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Z42" t="n">
         <v>450.8736</v>
       </c>
-      <c r="R42" t="n">
+      <c r="AA42" t="n">
         <v>429.5215</v>
       </c>
-      <c r="S42" t="n">
+      <c r="AB42" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T42" t="n">
+      <c r="AC42" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5077,58 +7126,85 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>41.345</v>
+      </c>
+      <c r="C43" t="n">
+        <v>41.715</v>
+      </c>
+      <c r="D43" t="n">
+        <v>40.905</v>
+      </c>
+      <c r="E43" t="n">
         <v>41.415</v>
       </c>
-      <c r="C43" t="n">
+      <c r="F43" t="n">
         <v>38.5608</v>
       </c>
-      <c r="D43" t="n">
+      <c r="G43" t="n">
         <v>35.3717</v>
       </c>
-      <c r="E43" t="n">
+      <c r="H43" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F43" t="n">
+      <c r="I43" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>11 sep</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="L43" t="n">
+        <v>175.68</v>
+      </c>
+      <c r="M43" t="n">
+        <v>178.84</v>
+      </c>
+      <c r="N43" t="n">
+        <v>172.16</v>
+      </c>
+      <c r="O43" t="n">
         <v>177.26</v>
       </c>
-      <c r="J43" t="n">
+      <c r="P43" t="n">
         <v>165.5248</v>
       </c>
-      <c r="K43" t="n">
+      <c r="Q43" t="n">
         <v>165.9594</v>
       </c>
-      <c r="L43" t="n">
+      <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M43" t="n">
+      <c r="S43" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>11 sep</t>
         </is>
       </c>
-      <c r="P43" t="n">
+      <c r="V43" t="n">
+        <v>495.65</v>
+      </c>
+      <c r="W43" t="n">
+        <v>498.97</v>
+      </c>
+      <c r="X43" t="n">
+        <v>492.58</v>
+      </c>
+      <c r="Y43" t="n">
         <v>495.63</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Z43" t="n">
         <v>453.115</v>
       </c>
-      <c r="R43" t="n">
-        <v>429.654</v>
-      </c>
-      <c r="S43" t="n">
+      <c r="AA43" t="n">
+        <v>429.6539</v>
+      </c>
+      <c r="AB43" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T43" t="n">
+      <c r="AC43" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5139,58 +7215,85 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="C44" t="n">
+        <v>42.285</v>
+      </c>
+      <c r="D44" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E44" t="n">
         <v>41.91</v>
       </c>
-      <c r="C44" t="n">
+      <c r="F44" t="n">
         <v>38.7226</v>
       </c>
-      <c r="D44" t="n">
+      <c r="G44" t="n">
         <v>35.4269</v>
       </c>
-      <c r="E44" t="n">
+      <c r="H44" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F44" t="n">
+      <c r="I44" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>14 sep</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="L44" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="M44" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="N44" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="O44" t="n">
         <v>186.26</v>
       </c>
-      <c r="J44" t="n">
+      <c r="P44" t="n">
         <v>166.4488</v>
       </c>
-      <c r="K44" t="n">
+      <c r="Q44" t="n">
         <v>165.8745</v>
       </c>
-      <c r="L44" t="n">
+      <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M44" t="n">
+      <c r="S44" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>14 sep</t>
         </is>
       </c>
-      <c r="P44" t="n">
+      <c r="V44" t="n">
+        <v>497.06</v>
+      </c>
+      <c r="W44" t="n">
+        <v>509.95</v>
+      </c>
+      <c r="X44" t="n">
+        <v>495.34</v>
+      </c>
+      <c r="Y44" t="n">
         <v>505.41</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Z44" t="n">
         <v>455.4281</v>
       </c>
-      <c r="R44" t="n">
+      <c r="AA44" t="n">
         <v>429.8259</v>
       </c>
-      <c r="S44" t="n">
+      <c r="AB44" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T44" t="n">
+      <c r="AC44" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5201,58 +7304,85 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>41.845</v>
+      </c>
+      <c r="C45" t="n">
         <v>42.7</v>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="E45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="F45" t="n">
         <v>38.8782</v>
       </c>
-      <c r="D45" t="n">
+      <c r="G45" t="n">
         <v>35.4854</v>
       </c>
-      <c r="E45" t="n">
+      <c r="H45" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F45" t="n">
+      <c r="I45" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>15 sep</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="L45" t="n">
+        <v>186.64</v>
+      </c>
+      <c r="M45" t="n">
+        <v>187.26</v>
+      </c>
+      <c r="N45" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="O45" t="n">
         <v>187.08</v>
       </c>
-      <c r="J45" t="n">
+      <c r="P45" t="n">
         <v>167.3124</v>
       </c>
-      <c r="K45" t="n">
+      <c r="Q45" t="n">
         <v>165.7921</v>
       </c>
-      <c r="L45" t="n">
+      <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M45" t="n">
+      <c r="S45" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>15 sep</t>
         </is>
       </c>
-      <c r="P45" t="n">
+      <c r="V45" t="n">
+        <v>500.06</v>
+      </c>
+      <c r="W45" t="n">
+        <v>505.9</v>
+      </c>
+      <c r="X45" t="n">
+        <v>495.54</v>
+      </c>
+      <c r="Y45" t="n">
         <v>497.12</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Z45" t="n">
         <v>457.6502</v>
       </c>
-      <c r="R45" t="n">
+      <c r="AA45" t="n">
         <v>429.9416</v>
       </c>
-      <c r="S45" t="n">
+      <c r="AB45" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T45" t="n">
+      <c r="AC45" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5263,58 +7393,85 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="C46" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="D46" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E46" t="n">
         <v>41.825</v>
       </c>
-      <c r="C46" t="n">
+      <c r="F46" t="n">
         <v>38.9989</v>
       </c>
-      <c r="D46" t="n">
+      <c r="G46" t="n">
         <v>35.5403</v>
       </c>
-      <c r="E46" t="n">
+      <c r="H46" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F46" t="n">
+      <c r="I46" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>16 sep</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="L46" t="n">
+        <v>185.86</v>
+      </c>
+      <c r="M46" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="N46" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="O46" t="n">
         <v>186.56</v>
       </c>
-      <c r="J46" t="n">
+      <c r="P46" t="n">
         <v>168.2844</v>
       </c>
-      <c r="K46" t="n">
+      <c r="Q46" t="n">
         <v>165.6996</v>
       </c>
-      <c r="L46" t="n">
+      <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M46" t="n">
+      <c r="S46" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>16 sep</t>
         </is>
       </c>
-      <c r="P46" t="n">
+      <c r="V46" t="n">
+        <v>493.03</v>
+      </c>
+      <c r="W46" t="n">
+        <v>495.97</v>
+      </c>
+      <c r="X46" t="n">
+        <v>487.23</v>
+      </c>
+      <c r="Y46" t="n">
         <v>490.3</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Z46" t="n">
         <v>459.694</v>
       </c>
-      <c r="R46" t="n">
+      <c r="AA46" t="n">
         <v>429.9809</v>
       </c>
-      <c r="S46" t="n">
+      <c r="AB46" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T46" t="n">
+      <c r="AC46" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5325,58 +7482,85 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="C47" t="n">
+        <v>42.055</v>
+      </c>
+      <c r="D47" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="E47" t="n">
         <v>41.56</v>
       </c>
-      <c r="C47" t="n">
+      <c r="F47" t="n">
         <v>39.1225</v>
       </c>
-      <c r="D47" t="n">
+      <c r="G47" t="n">
         <v>35.5926</v>
       </c>
-      <c r="E47" t="n">
+      <c r="H47" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F47" t="n">
+      <c r="I47" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>17 sep</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="L47" t="n">
+        <v>188.54</v>
+      </c>
+      <c r="M47" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>184.62</v>
+      </c>
+      <c r="O47" t="n">
         <v>188</v>
       </c>
-      <c r="J47" t="n">
+      <c r="P47" t="n">
         <v>169.2896</v>
       </c>
-      <c r="K47" t="n">
+      <c r="Q47" t="n">
         <v>165.6125</v>
       </c>
-      <c r="L47" t="n">
+      <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M47" t="n">
+      <c r="S47" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>17 sep</t>
         </is>
       </c>
-      <c r="P47" t="n">
+      <c r="V47" t="n">
+        <v>497.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>501.47</v>
+      </c>
+      <c r="X47" t="n">
+        <v>493.17</v>
+      </c>
+      <c r="Y47" t="n">
         <v>497.75</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Z47" t="n">
         <v>461.9966</v>
       </c>
-      <c r="R47" t="n">
+      <c r="AA47" t="n">
         <v>430.0251</v>
       </c>
-      <c r="S47" t="n">
+      <c r="AB47" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T47" t="n">
+      <c r="AC47" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5387,58 +7571,85 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>41.465</v>
+      </c>
+      <c r="C48" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>40.955</v>
+      </c>
+      <c r="E48" t="n">
         <v>41.315</v>
       </c>
-      <c r="C48" t="n">
+      <c r="F48" t="n">
         <v>39.2414</v>
       </c>
-      <c r="D48" t="n">
+      <c r="G48" t="n">
         <v>35.6436</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>18 sep</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>187.26</v>
+      </c>
+      <c r="N48" t="n">
+        <v>182.56</v>
+      </c>
+      <c r="O48" t="n">
         <v>183.12</v>
       </c>
-      <c r="J48" t="n">
+      <c r="P48" t="n">
         <v>170.2004</v>
       </c>
-      <c r="K48" t="n">
+      <c r="Q48" t="n">
         <v>165.5062</v>
       </c>
-      <c r="L48" t="n">
+      <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M48" t="n">
+      <c r="S48" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>18 sep</t>
         </is>
       </c>
-      <c r="P48" t="n">
+      <c r="V48" t="n">
+        <v>497.97</v>
+      </c>
+      <c r="W48" t="n">
+        <v>498.65</v>
+      </c>
+      <c r="X48" t="n">
+        <v>491.1</v>
+      </c>
+      <c r="Y48" t="n">
         <v>493.78</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Z48" t="n">
         <v>464.1995</v>
       </c>
-      <c r="R48" t="n">
+      <c r="AA48" t="n">
         <v>430.0757</v>
       </c>
-      <c r="S48" t="n">
+      <c r="AB48" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T48" t="n">
+      <c r="AC48" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5449,58 +7660,85 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="C49" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="D49" t="n">
         <v>40.775</v>
       </c>
-      <c r="C49" t="n">
+      <c r="E49" t="n">
+        <v>40.775</v>
+      </c>
+      <c r="F49" t="n">
         <v>39.3341</v>
       </c>
-      <c r="D49" t="n">
+      <c r="G49" t="n">
         <v>35.6939</v>
       </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F49" t="n">
+      <c r="I49" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>21 sep</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="L49" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="M49" t="n">
+        <v>185.86</v>
+      </c>
+      <c r="N49" t="n">
+        <v>182.48</v>
+      </c>
+      <c r="O49" t="n">
         <v>182.86</v>
       </c>
-      <c r="J49" t="n">
+      <c r="P49" t="n">
         <v>171.0432</v>
       </c>
-      <c r="K49" t="n">
+      <c r="Q49" t="n">
         <v>165.4052</v>
       </c>
-      <c r="L49" t="n">
+      <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M49" t="n">
+      <c r="S49" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>21 sep</t>
         </is>
       </c>
-      <c r="P49" t="n">
+      <c r="V49" t="n">
+        <v>494.95</v>
+      </c>
+      <c r="W49" t="n">
+        <v>501.87</v>
+      </c>
+      <c r="X49" t="n">
+        <v>491.33</v>
+      </c>
+      <c r="Y49" t="n">
         <v>501.61</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Z49" t="n">
         <v>466.5442</v>
       </c>
-      <c r="R49" t="n">
+      <c r="AA49" t="n">
         <v>430.1492</v>
       </c>
-      <c r="S49" t="n">
+      <c r="AB49" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T49" t="n">
+      <c r="AC49" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5511,58 +7749,85 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="C50" t="n">
+        <v>41.165</v>
+      </c>
+      <c r="D50" t="n">
+        <v>40.215</v>
+      </c>
+      <c r="E50" t="n">
         <v>41.01</v>
       </c>
-      <c r="C50" t="n">
+      <c r="F50" t="n">
         <v>39.4244</v>
       </c>
-      <c r="D50" t="n">
+      <c r="G50" t="n">
         <v>35.746</v>
       </c>
-      <c r="E50" t="n">
+      <c r="H50" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F50" t="n">
+      <c r="I50" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>22 sep</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="L50" t="n">
+        <v>182.14</v>
+      </c>
+      <c r="M50" t="n">
+        <v>187.48</v>
+      </c>
+      <c r="N50" t="n">
+        <v>181.52</v>
+      </c>
+      <c r="O50" t="n">
         <v>182.32</v>
       </c>
-      <c r="J50" t="n">
+      <c r="P50" t="n">
         <v>171.9552</v>
       </c>
-      <c r="K50" t="n">
+      <c r="Q50" t="n">
         <v>165.2836</v>
       </c>
-      <c r="L50" t="n">
+      <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M50" t="n">
+      <c r="S50" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>22 sep</t>
         </is>
       </c>
-      <c r="P50" t="n">
+      <c r="V50" t="n">
+        <v>507.32</v>
+      </c>
+      <c r="W50" t="n">
+        <v>508.5</v>
+      </c>
+      <c r="X50" t="n">
+        <v>493.65</v>
+      </c>
+      <c r="Y50" t="n">
         <v>498</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Z50" t="n">
         <v>468.699</v>
       </c>
-      <c r="R50" t="n">
+      <c r="AA50" t="n">
         <v>430.2656</v>
       </c>
-      <c r="S50" t="n">
+      <c r="AB50" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T50" t="n">
+      <c r="AC50" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5573,58 +7838,85 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>41</v>
+      </c>
+      <c r="C51" t="n">
+        <v>41.755</v>
+      </c>
+      <c r="D51" t="n">
+        <v>40.995</v>
+      </c>
+      <c r="E51" t="n">
         <v>41.69</v>
       </c>
-      <c r="C51" t="n">
+      <c r="F51" t="n">
         <v>39.5272</v>
       </c>
-      <c r="D51" t="n">
+      <c r="G51" t="n">
         <v>35.8024</v>
       </c>
-      <c r="E51" t="n">
+      <c r="H51" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F51" t="n">
+      <c r="I51" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>23 sep</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="L51" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="M51" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>183.48</v>
+      </c>
+      <c r="O51" t="n">
         <v>186.46</v>
       </c>
-      <c r="J51" t="n">
+      <c r="P51" t="n">
         <v>172.9448</v>
       </c>
-      <c r="K51" t="n">
+      <c r="Q51" t="n">
         <v>165.1675</v>
       </c>
-      <c r="L51" t="n">
+      <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M51" t="n">
+      <c r="S51" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>23 sep</t>
         </is>
       </c>
-      <c r="P51" t="n">
+      <c r="V51" t="n">
+        <v>500.76</v>
+      </c>
+      <c r="W51" t="n">
+        <v>509.44</v>
+      </c>
+      <c r="X51" t="n">
+        <v>495.88</v>
+      </c>
+      <c r="Y51" t="n">
         <v>500.59</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Z51" t="n">
         <v>471.0267</v>
       </c>
-      <c r="R51" t="n">
+      <c r="AA51" t="n">
         <v>430.3795</v>
       </c>
-      <c r="S51" t="n">
+      <c r="AB51" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T51" t="n">
+      <c r="AC51" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5635,58 +7927,85 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>41.825</v>
+      </c>
+      <c r="C52" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="D52" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="E52" t="n">
         <v>42.43</v>
       </c>
-      <c r="C52" t="n">
+      <c r="F52" t="n">
         <v>39.6382</v>
       </c>
-      <c r="D52" t="n">
+      <c r="G52" t="n">
         <v>35.8638</v>
       </c>
-      <c r="E52" t="n">
+      <c r="H52" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F52" t="n">
+      <c r="I52" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>24 sep</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="L52" t="n">
+        <v>184.52</v>
+      </c>
+      <c r="M52" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>182.26</v>
+      </c>
+      <c r="O52" t="n">
         <v>184.18</v>
       </c>
-      <c r="J52" t="n">
+      <c r="P52" t="n">
         <v>173.8756</v>
       </c>
-      <c r="K52" t="n">
+      <c r="Q52" t="n">
         <v>165.0554</v>
       </c>
-      <c r="L52" t="n">
+      <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M52" t="n">
+      <c r="S52" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>24 sep</t>
         </is>
       </c>
-      <c r="P52" t="n">
+      <c r="V52" t="n">
+        <v>495.07</v>
+      </c>
+      <c r="W52" t="n">
+        <v>498.9</v>
+      </c>
+      <c r="X52" t="n">
+        <v>491.22</v>
+      </c>
+      <c r="Y52" t="n">
         <v>497.93</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Z52" t="n">
         <v>473.0876</v>
       </c>
-      <c r="R52" t="n">
+      <c r="AA52" t="n">
         <v>430.4686</v>
       </c>
-      <c r="S52" t="n">
+      <c r="AB52" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T52" t="n">
+      <c r="AC52" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5697,58 +8016,85 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="C53" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="D53" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="E53" t="n">
         <v>42.06</v>
       </c>
-      <c r="C53" t="n">
+      <c r="F53" t="n">
         <v>39.7263</v>
       </c>
-      <c r="D53" t="n">
+      <c r="G53" t="n">
         <v>35.9239</v>
       </c>
-      <c r="E53" t="n">
+      <c r="H53" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F53" t="n">
+      <c r="I53" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>25 sep</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="L53" t="n">
+        <v>184.42</v>
+      </c>
+      <c r="M53" t="n">
         <v>185.92</v>
       </c>
-      <c r="J53" t="n">
+      <c r="N53" t="n">
+        <v>183.76</v>
+      </c>
+      <c r="O53" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="P53" t="n">
         <v>174.8356</v>
       </c>
-      <c r="K53" t="n">
+      <c r="Q53" t="n">
         <v>164.9525</v>
       </c>
-      <c r="L53" t="n">
+      <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M53" t="n">
+      <c r="S53" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>25 sep</t>
         </is>
       </c>
-      <c r="P53" t="n">
+      <c r="V53" t="n">
+        <v>499.04</v>
+      </c>
+      <c r="W53" t="n">
+        <v>519.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>497.25</v>
+      </c>
+      <c r="Y53" t="n">
         <v>516.17</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Z53" t="n">
         <v>475.4041</v>
       </c>
-      <c r="R53" t="n">
+      <c r="AA53" t="n">
         <v>430.6098</v>
       </c>
-      <c r="S53" t="n">
+      <c r="AB53" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T53" t="n">
+      <c r="AC53" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5759,58 +8105,85 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="C54" t="n">
+        <v>42.995</v>
+      </c>
+      <c r="D54" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="E54" t="n">
         <v>42.725</v>
       </c>
-      <c r="C54" t="n">
+      <c r="F54" t="n">
         <v>39.8301</v>
       </c>
-      <c r="D54" t="n">
+      <c r="G54" t="n">
         <v>35.9888</v>
       </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F54" t="n">
+      <c r="I54" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>28 sep</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="L54" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="N54" t="n">
+        <v>178.88</v>
+      </c>
+      <c r="O54" t="n">
         <v>184.02</v>
       </c>
-      <c r="J54" t="n">
+      <c r="P54" t="n">
         <v>175.7508</v>
       </c>
-      <c r="K54" t="n">
+      <c r="Q54" t="n">
         <v>164.8355</v>
       </c>
-      <c r="L54" t="n">
+      <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M54" t="n">
+      <c r="S54" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>28 sep</t>
         </is>
       </c>
-      <c r="P54" t="n">
+      <c r="V54" t="n">
+        <v>505.47</v>
+      </c>
+      <c r="W54" t="n">
+        <v>513.33</v>
+      </c>
+      <c r="X54" t="n">
+        <v>502.22</v>
+      </c>
+      <c r="Y54" t="n">
         <v>509.22</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Z54" t="n">
         <v>477.7269</v>
       </c>
-      <c r="R54" t="n">
+      <c r="AA54" t="n">
         <v>430.7113</v>
       </c>
-      <c r="S54" t="n">
+      <c r="AB54" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T54" t="n">
+      <c r="AC54" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5821,58 +8194,85 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="C55" t="n">
+        <v>42.665</v>
+      </c>
+      <c r="D55" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="E55" t="n">
         <v>42.05</v>
       </c>
-      <c r="C55" t="n">
+      <c r="F55" t="n">
         <v>39.9146</v>
       </c>
-      <c r="D55" t="n">
+      <c r="G55" t="n">
         <v>36.0498</v>
       </c>
-      <c r="E55" t="n">
+      <c r="H55" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F55" t="n">
+      <c r="I55" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>29 sep</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="L55" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="M55" t="n">
+        <v>186.34</v>
+      </c>
+      <c r="N55" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="O55" t="n">
         <v>185.32</v>
       </c>
-      <c r="J55" t="n">
+      <c r="P55" t="n">
         <v>176.7288</v>
       </c>
-      <c r="K55" t="n">
+      <c r="Q55" t="n">
         <v>164.733</v>
       </c>
-      <c r="L55" t="n">
+      <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M55" t="n">
+      <c r="S55" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>29 sep</t>
         </is>
       </c>
-      <c r="P55" t="n">
+      <c r="V55" t="n">
+        <v>508.31</v>
+      </c>
+      <c r="W55" t="n">
+        <v>513.64</v>
+      </c>
+      <c r="X55" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="Y55" t="n">
         <v>508.96</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Z55" t="n">
         <v>479.8754</v>
       </c>
-      <c r="R55" t="n">
+      <c r="AA55" t="n">
         <v>430.8784</v>
       </c>
-      <c r="S55" t="n">
+      <c r="AB55" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T55" t="n">
+      <c r="AC55" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5883,58 +8283,85 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>41.975</v>
+      </c>
+      <c r="C56" t="n">
+        <v>42.095</v>
+      </c>
+      <c r="D56" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="E56" t="n">
         <v>41.91</v>
       </c>
-      <c r="C56" t="n">
+      <c r="F56" t="n">
         <v>39.9874</v>
       </c>
-      <c r="D56" t="n">
+      <c r="G56" t="n">
         <v>36.1135</v>
       </c>
-      <c r="E56" t="n">
+      <c r="H56" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F56" t="n">
+      <c r="I56" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>30 sep</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="L56" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>181.06</v>
+      </c>
+      <c r="O56" t="n">
         <v>185.66</v>
       </c>
-      <c r="J56" t="n">
+      <c r="P56" t="n">
         <v>177.8012</v>
       </c>
-      <c r="K56" t="n">
+      <c r="Q56" t="n">
         <v>164.6377</v>
       </c>
-      <c r="L56" t="n">
+      <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M56" t="n">
+      <c r="S56" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>30 sep</t>
         </is>
       </c>
-      <c r="P56" t="n">
+      <c r="V56" t="n">
+        <v>511.61</v>
+      </c>
+      <c r="W56" t="n">
+        <v>519.83</v>
+      </c>
+      <c r="X56" t="n">
+        <v>510.31</v>
+      </c>
+      <c r="Y56" t="n">
         <v>512.9</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Z56" t="n">
         <v>482.1933</v>
       </c>
-      <c r="R56" t="n">
+      <c r="AA56" t="n">
         <v>431.0408</v>
       </c>
-      <c r="S56" t="n">
+      <c r="AB56" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T56" t="n">
+      <c r="AC56" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -5945,58 +8372,85 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>41.625</v>
+      </c>
+      <c r="C57" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="D57" t="n">
+        <v>41.165</v>
+      </c>
+      <c r="E57" t="n">
         <v>42.24</v>
       </c>
-      <c r="C57" t="n">
+      <c r="F57" t="n">
         <v>40.0562</v>
       </c>
-      <c r="D57" t="n">
+      <c r="G57" t="n">
         <v>36.1777</v>
       </c>
-      <c r="E57" t="n">
+      <c r="H57" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F57" t="n">
+      <c r="I57" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>1 okt</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="L57" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="M57" t="n">
+        <v>190.26</v>
+      </c>
+      <c r="N57" t="n">
+        <v>181.34</v>
+      </c>
+      <c r="O57" t="n">
         <v>186.74</v>
       </c>
-      <c r="J57" t="n">
+      <c r="P57" t="n">
         <v>178.9696</v>
       </c>
-      <c r="K57" t="n">
+      <c r="Q57" t="n">
         <v>164.5407</v>
       </c>
-      <c r="L57" t="n">
+      <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M57" t="n">
+      <c r="S57" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>1 okt</t>
         </is>
       </c>
-      <c r="P57" t="n">
+      <c r="V57" t="n">
+        <v>519.88</v>
+      </c>
+      <c r="W57" t="n">
+        <v>522.85</v>
+      </c>
+      <c r="X57" t="n">
+        <v>512.17</v>
+      </c>
+      <c r="Y57" t="n">
         <v>512.8</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Z57" t="n">
         <v>484.6572</v>
       </c>
-      <c r="R57" t="n">
+      <c r="AA57" t="n">
         <v>431.2272</v>
       </c>
-      <c r="S57" t="n">
+      <c r="AB57" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T57" t="n">
+      <c r="AC57" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6007,58 +8461,85 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="C58" t="n">
+        <v>42.745</v>
+      </c>
+      <c r="D58" t="n">
+        <v>41.985</v>
+      </c>
+      <c r="E58" t="n">
         <v>42.4</v>
       </c>
-      <c r="C58" t="n">
+      <c r="F58" t="n">
         <v>40.1364</v>
       </c>
-      <c r="D58" t="n">
+      <c r="G58" t="n">
         <v>36.2422</v>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F58" t="n">
+      <c r="I58" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>2 okt</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="L58" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="M58" t="n">
+        <v>188.74</v>
+      </c>
+      <c r="N58" t="n">
         <v>183.92</v>
       </c>
-      <c r="J58" t="n">
+      <c r="O58" t="n">
+        <v>183.92</v>
+      </c>
+      <c r="P58" t="n">
         <v>179.844</v>
       </c>
-      <c r="K58" t="n">
+      <c r="Q58" t="n">
         <v>164.4442</v>
       </c>
-      <c r="L58" t="n">
+      <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M58" t="n">
+      <c r="S58" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>2 okt</t>
         </is>
       </c>
-      <c r="P58" t="n">
+      <c r="V58" t="n">
+        <v>519.39</v>
+      </c>
+      <c r="W58" t="n">
+        <v>522.5</v>
+      </c>
+      <c r="X58" t="n">
+        <v>513.66</v>
+      </c>
+      <c r="Y58" t="n">
         <v>517.53</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Z58" t="n">
         <v>487.3905</v>
       </c>
-      <c r="R58" t="n">
+      <c r="AA58" t="n">
         <v>431.4557</v>
       </c>
-      <c r="S58" t="n">
+      <c r="AB58" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T58" t="n">
+      <c r="AC58" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6069,58 +8550,85 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>42.645</v>
+      </c>
+      <c r="C59" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="D59" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="E59" t="n">
         <v>42.865</v>
       </c>
-      <c r="C59" t="n">
+      <c r="F59" t="n">
         <v>40.2347</v>
       </c>
-      <c r="D59" t="n">
+      <c r="G59" t="n">
         <v>36.3069</v>
       </c>
-      <c r="E59" t="n">
+      <c r="H59" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F59" t="n">
+      <c r="I59" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>5 okt</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="L59" t="n">
+        <v>185.06</v>
+      </c>
+      <c r="M59" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="N59" t="n">
+        <v>184.66</v>
+      </c>
+      <c r="O59" t="n">
         <v>185.04</v>
       </c>
-      <c r="J59" t="n">
+      <c r="P59" t="n">
         <v>180.5192</v>
       </c>
-      <c r="K59" t="n">
+      <c r="Q59" t="n">
         <v>164.3515</v>
       </c>
-      <c r="L59" t="n">
+      <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M59" t="n">
+      <c r="S59" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>5 okt</t>
         </is>
       </c>
-      <c r="P59" t="n">
+      <c r="V59" t="n">
+        <v>521.62</v>
+      </c>
+      <c r="W59" t="n">
+        <v>532.35</v>
+      </c>
+      <c r="X59" t="n">
+        <v>521.47</v>
+      </c>
+      <c r="Y59" t="n">
         <v>525.1799999999999</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Z59" t="n">
         <v>490.2745</v>
       </c>
-      <c r="R59" t="n">
+      <c r="AA59" t="n">
         <v>431.7147</v>
       </c>
-      <c r="S59" t="n">
+      <c r="AB59" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T59" t="n">
+      <c r="AC59" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6131,58 +8639,85 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="C60" t="n">
+        <v>43.285</v>
+      </c>
+      <c r="D60" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="E60" t="n">
         <v>43.185</v>
       </c>
-      <c r="C60" t="n">
+      <c r="F60" t="n">
         <v>40.349</v>
       </c>
-      <c r="D60" t="n">
+      <c r="G60" t="n">
         <v>36.3726</v>
       </c>
-      <c r="E60" t="n">
+      <c r="H60" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F60" t="n">
+      <c r="I60" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>6 okt</t>
         </is>
       </c>
-      <c r="I60" t="n">
+      <c r="L60" t="n">
+        <v>186.56</v>
+      </c>
+      <c r="M60" t="n">
+        <v>190.22</v>
+      </c>
+      <c r="N60" t="n">
+        <v>186.06</v>
+      </c>
+      <c r="O60" t="n">
         <v>188.6</v>
       </c>
-      <c r="J60" t="n">
+      <c r="P60" t="n">
         <v>181.1064</v>
       </c>
-      <c r="K60" t="n">
+      <c r="Q60" t="n">
         <v>164.2647</v>
       </c>
-      <c r="L60" t="n">
+      <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M60" t="n">
+      <c r="S60" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>6 okt</t>
         </is>
       </c>
-      <c r="P60" t="n">
+      <c r="V60" t="n">
+        <v>531.6799999999999</v>
+      </c>
+      <c r="W60" t="n">
+        <v>535.6900000000001</v>
+      </c>
+      <c r="X60" t="n">
+        <v>528.78</v>
+      </c>
+      <c r="Y60" t="n">
         <v>529.3</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="Z60" t="n">
         <v>493.0931</v>
       </c>
-      <c r="R60" t="n">
+      <c r="AA60" t="n">
         <v>431.9956</v>
       </c>
-      <c r="S60" t="n">
+      <c r="AB60" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T60" t="n">
+      <c r="AC60" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6193,58 +8728,85 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="C61" t="n">
+        <v>43.835</v>
+      </c>
+      <c r="D61" t="n">
+        <v>43.145</v>
+      </c>
+      <c r="E61" t="n">
         <v>43.25</v>
       </c>
-      <c r="C61" t="n">
+      <c r="F61" t="n">
         <v>40.4451</v>
       </c>
-      <c r="D61" t="n">
+      <c r="G61" t="n">
         <v>36.4388</v>
       </c>
-      <c r="E61" t="n">
+      <c r="H61" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F61" t="n">
+      <c r="I61" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>7 okt</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="L61" t="n">
+        <v>187</v>
+      </c>
+      <c r="M61" t="n">
+        <v>188.72</v>
+      </c>
+      <c r="N61" t="n">
+        <v>186.04</v>
+      </c>
+      <c r="O61" t="n">
         <v>187.62</v>
       </c>
-      <c r="J61" t="n">
+      <c r="P61" t="n">
         <v>181.618</v>
       </c>
-      <c r="K61" t="n">
+      <c r="Q61" t="n">
         <v>164.1762</v>
       </c>
-      <c r="L61" t="n">
+      <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M61" t="n">
+      <c r="S61" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>7 okt</t>
         </is>
       </c>
-      <c r="P61" t="n">
+      <c r="V61" t="n">
+        <v>530.73</v>
+      </c>
+      <c r="W61" t="n">
+        <v>531.73</v>
+      </c>
+      <c r="X61" t="n">
+        <v>524.6900000000001</v>
+      </c>
+      <c r="Y61" t="n">
         <v>529.76</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="Z61" t="n">
         <v>495.8361</v>
       </c>
-      <c r="R61" t="n">
+      <c r="AA61" t="n">
         <v>432.2398</v>
       </c>
-      <c r="S61" t="n">
+      <c r="AB61" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T61" t="n">
+      <c r="AC61" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6255,58 +8817,85 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>43.555</v>
+      </c>
+      <c r="C62" t="n">
+        <v>44.815</v>
+      </c>
+      <c r="D62" t="n">
+        <v>43.5425</v>
+      </c>
+      <c r="E62" t="n">
         <v>44.75</v>
       </c>
-      <c r="C62" t="n">
+      <c r="F62" t="n">
         <v>40.5699</v>
       </c>
-      <c r="D62" t="n">
+      <c r="G62" t="n">
         <v>36.5123</v>
       </c>
-      <c r="E62" t="n">
+      <c r="H62" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F62" t="n">
+      <c r="I62" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>8 okt</t>
         </is>
       </c>
-      <c r="I62" t="n">
+      <c r="L62" t="n">
+        <v>187.04</v>
+      </c>
+      <c r="M62" t="n">
+        <v>189.82</v>
+      </c>
+      <c r="N62" t="n">
+        <v>183.76</v>
+      </c>
+      <c r="O62" t="n">
         <v>184.62</v>
       </c>
-      <c r="J62" t="n">
+      <c r="P62" t="n">
         <v>182.192</v>
       </c>
-      <c r="K62" t="n">
+      <c r="Q62" t="n">
         <v>164.074</v>
       </c>
-      <c r="L62" t="n">
+      <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M62" t="n">
+      <c r="S62" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>8 okt</t>
         </is>
       </c>
-      <c r="P62" t="n">
+      <c r="V62" t="n">
+        <v>529.8099999999999</v>
+      </c>
+      <c r="W62" t="n">
+        <v>533.51</v>
+      </c>
+      <c r="X62" t="n">
+        <v>518.79</v>
+      </c>
+      <c r="Y62" t="n">
         <v>522.61</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="Z62" t="n">
         <v>498.4921</v>
       </c>
-      <c r="R62" t="n">
+      <c r="AA62" t="n">
         <v>432.4385</v>
       </c>
-      <c r="S62" t="n">
+      <c r="AB62" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T62" t="n">
+      <c r="AC62" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6317,58 +8906,85 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="C63" t="n">
+        <v>45.155</v>
+      </c>
+      <c r="D63" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="E63" t="n">
         <v>45.035</v>
       </c>
-      <c r="C63" t="n">
+      <c r="F63" t="n">
         <v>40.6842</v>
       </c>
-      <c r="D63" t="n">
+      <c r="G63" t="n">
         <v>36.5866</v>
       </c>
-      <c r="E63" t="n">
+      <c r="H63" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F63" t="n">
+      <c r="I63" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>9 okt</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="L63" t="n">
+        <v>188.98</v>
+      </c>
+      <c r="M63" t="n">
+        <v>192.58</v>
+      </c>
+      <c r="N63" t="n">
+        <v>188.86</v>
+      </c>
+      <c r="O63" t="n">
         <v>191.46</v>
       </c>
-      <c r="J63" t="n">
+      <c r="P63" t="n">
         <v>182.8676</v>
       </c>
-      <c r="K63" t="n">
+      <c r="Q63" t="n">
         <v>164.0101</v>
       </c>
-      <c r="L63" t="n">
+      <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M63" t="n">
+      <c r="S63" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>9 okt</t>
         </is>
       </c>
-      <c r="P63" t="n">
+      <c r="V63" t="n">
+        <v>528.24</v>
+      </c>
+      <c r="W63" t="n">
+        <v>537.22</v>
+      </c>
+      <c r="X63" t="n">
+        <v>526.24</v>
+      </c>
+      <c r="Y63" t="n">
         <v>535.0700000000001</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Z63" t="n">
         <v>500.1885</v>
       </c>
-      <c r="R63" t="n">
+      <c r="AA63" t="n">
         <v>432.7046</v>
       </c>
-      <c r="S63" t="n">
+      <c r="AB63" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T63" t="n">
+      <c r="AC63" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6379,58 +8995,85 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>44.725</v>
+      </c>
+      <c r="C64" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="D64" t="n">
+        <v>44.695</v>
+      </c>
+      <c r="E64" t="n">
         <v>45.56</v>
       </c>
-      <c r="C64" t="n">
+      <c r="F64" t="n">
         <v>40.8072</v>
       </c>
-      <c r="D64" t="n">
+      <c r="G64" t="n">
         <v>36.6625</v>
       </c>
-      <c r="E64" t="n">
+      <c r="H64" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F64" t="n">
+      <c r="I64" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>12 okt</t>
         </is>
       </c>
-      <c r="I64" t="n">
+      <c r="L64" t="n">
+        <v>190.58</v>
+      </c>
+      <c r="M64" t="n">
+        <v>197.88</v>
+      </c>
+      <c r="N64" t="n">
+        <v>189.78</v>
+      </c>
+      <c r="O64" t="n">
         <v>194.46</v>
       </c>
-      <c r="J64" t="n">
+      <c r="P64" t="n">
         <v>183.464</v>
       </c>
-      <c r="K64" t="n">
+      <c r="Q64" t="n">
         <v>163.9576</v>
       </c>
-      <c r="L64" t="n">
+      <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M64" t="n">
+      <c r="S64" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>12 okt</t>
         </is>
       </c>
-      <c r="P64" t="n">
+      <c r="V64" t="n">
+        <v>537.53</v>
+      </c>
+      <c r="W64" t="n">
+        <v>542.74</v>
+      </c>
+      <c r="X64" t="n">
+        <v>535.7</v>
+      </c>
+      <c r="Y64" t="n">
         <v>541.15</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Z64" t="n">
         <v>501.7346</v>
       </c>
-      <c r="R64" t="n">
+      <c r="AA64" t="n">
         <v>432.9914</v>
       </c>
-      <c r="S64" t="n">
+      <c r="AB64" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T64" t="n">
+      <c r="AC64" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6441,58 +9084,85 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="C65" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="D65" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="E65" t="n">
         <v>45.95</v>
       </c>
-      <c r="C65" t="n">
+      <c r="F65" t="n">
         <v>40.9565</v>
       </c>
-      <c r="D65" t="n">
+      <c r="G65" t="n">
         <v>36.7398</v>
       </c>
-      <c r="E65" t="n">
+      <c r="H65" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F65" t="n">
+      <c r="I65" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>13 okt</t>
         </is>
       </c>
-      <c r="I65" t="n">
+      <c r="L65" t="n">
+        <v>196</v>
+      </c>
+      <c r="M65" t="n">
+        <v>198.18</v>
+      </c>
+      <c r="N65" t="n">
+        <v>194.02</v>
+      </c>
+      <c r="O65" t="n">
         <v>197.28</v>
       </c>
-      <c r="J65" t="n">
+      <c r="P65" t="n">
         <v>184.062</v>
       </c>
-      <c r="K65" t="n">
+      <c r="Q65" t="n">
         <v>163.9196</v>
       </c>
-      <c r="L65" t="n">
+      <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M65" t="n">
+      <c r="S65" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>13 okt</t>
         </is>
       </c>
-      <c r="P65" t="n">
+      <c r="V65" t="n">
+        <v>544.64</v>
+      </c>
+      <c r="W65" t="n">
+        <v>551.15</v>
+      </c>
+      <c r="X65" t="n">
+        <v>543.0599999999999</v>
+      </c>
+      <c r="Y65" t="n">
         <v>543.45</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Z65" t="n">
         <v>502.8689</v>
       </c>
-      <c r="R65" t="n">
+      <c r="AA65" t="n">
         <v>433.2839</v>
       </c>
-      <c r="S65" t="n">
+      <c r="AB65" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T65" t="n">
+      <c r="AC65" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>
@@ -6503,58 +9173,85 @@
         </is>
       </c>
       <c r="B66" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="C66" t="n">
+        <v>46.675</v>
+      </c>
+      <c r="D66" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="E66" t="n">
         <v>46.455</v>
       </c>
-      <c r="C66" t="n">
+      <c r="F66" t="n">
         <v>41.125</v>
       </c>
-      <c r="D66" t="n">
+      <c r="G66" t="n">
         <v>36.8183</v>
       </c>
-      <c r="E66" t="n">
+      <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
-      <c r="F66" t="n">
+      <c r="I66" t="n">
         <v>43.73250225612095</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>14 okt</t>
         </is>
       </c>
-      <c r="I66" t="n">
+      <c r="L66" t="n">
+        <v>196.6</v>
+      </c>
+      <c r="M66" t="n">
+        <v>199.36</v>
+      </c>
+      <c r="N66" t="n">
+        <v>195.26</v>
+      </c>
+      <c r="O66" t="n">
         <v>196.94</v>
       </c>
-      <c r="J66" t="n">
+      <c r="P66" t="n">
         <v>184.6156</v>
       </c>
-      <c r="K66" t="n">
+      <c r="Q66" t="n">
         <v>163.9114</v>
       </c>
-      <c r="L66" t="n">
+      <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
-      <c r="M66" t="n">
+      <c r="S66" t="n">
         <v>181.0371344430106</v>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>14 okt</t>
         </is>
       </c>
-      <c r="P66" t="n">
+      <c r="V66" t="n">
+        <v>545.15</v>
+      </c>
+      <c r="W66" t="n">
+        <v>545.74</v>
+      </c>
+      <c r="X66" t="n">
+        <v>532.54</v>
+      </c>
+      <c r="Y66" t="n">
         <v>533.6900000000001</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Z66" t="n">
         <v>503.705</v>
       </c>
-      <c r="R66" t="n">
+      <c r="AA66" t="n">
         <v>433.5292</v>
       </c>
-      <c r="S66" t="n">
+      <c r="AB66" t="n">
         <v>535.3375423278808</v>
       </c>
-      <c r="T66" t="n">
+      <c r="AC66" t="n">
         <v>509.8989698529924</v>
       </c>
     </row>

--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,21 +40,26 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="0052514E"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000B0B0B"/>
-      <sz val="14"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B0B0B"/>
+      <sz val="13"/>
     </font>
     <font>
       <color rgb="0052514E"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -94,11 +99,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -592,8 +600,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1059,8 +1067,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1526,8 +1534,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1585,7 +1593,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1602,12 +1610,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1626,10 +1634,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -2064,381 +2072,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B67"/>
+  <dimension ref="B1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="135" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Grafieken van vandaag</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke kaars is één handelsdag: groen = die dag gestegen, rood = die dag gedaald; de dunne streep is de hoogste en laagste koers. Blauwe lijn = gemiddelde van 50 dagen, oranje = van 200 dagen, grijze stippellijn = instap, rode stippellijn = stop-loss (daar verkoopt de bot). Ga met de muis over een kaars of lijn voor de waarde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>1. Shell (SHELL.AS)  ·  46,46 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,73 zakt (-5,9%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="B2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00008300"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>▮ groen</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
+            <t xml:space="preserve"> = dag gestegen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00E34948"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>▮ rood</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
+            <t xml:space="preserve"> = dag gedaald    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="002A78D6"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>━ blauw</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
+            <t xml:space="preserve"> = gemiddelde 50 dagen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00EB6834"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>━ oranje</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
+            <t xml:space="preserve"> = gemiddelde 200 dagen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>╌ grijs</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = instap   </t>
+            <t xml:space="preserve"> = instap    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00E34948"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>╌ rood</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>2. SAP (SAP.DE)  ·  196,94 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ grijs</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = instap   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>3. Microsoft (MSFT)  ·  533,69 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ grijs</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = instap   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
-          </r>
+    <row r="3">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Elke kaars is één handelsdag; het dunne streepje loopt van de laagste naar de hoogste koers van die dag. Ga met de muis over een kaars of lijn om de waarde te zien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Trend-agent: open posities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Shell (SHELL.AS)  ·  46,46 EUR</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>SAP (SAP.DE)  ·  196,94 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,73 zakt (-5,9%).</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT)  ·  533,69 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7199,7 +6999,7 @@
         <v>453.115</v>
       </c>
       <c r="AA43" t="n">
-        <v>429.6539</v>
+        <v>429.654</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/voorbeeld/trend-agent.xlsx
+++ b/rapporten/voorbeeld/trend-agent.xlsx
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10026.55</v>
+        <v>10024.15</v>
       </c>
       <c r="C5" s="2">
         <f>B5-B4</f>
@@ -2213,12 +2213,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,73 zakt (-5,9%).</t>
+          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,70 zakt (-5,9%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
+          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,20 zakt (-8,0%).</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.73</v>
+        <v>43.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>181.04</v>
+        <v>181.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>421.046</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3185</v>
+        <v>429.3186</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5879,7 +5879,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>545.15</v>
+        <v>545.27</v>
       </c>
       <c r="W66" t="n">
-        <v>545.74</v>
+        <v>545.75</v>
       </c>
       <c r="X66" t="n">
         <v>532.54</v>
